--- a/GearSage-client/rate/excel/hook_detail.xlsx
+++ b/GearSage-client/rate/excel/hook_detail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O991"/>
+  <dimension ref="A1:O1162"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -46976,9 +46976,8046 @@
         <v/>
       </c>
     </row>
+    <row r="992">
+      <c r="A992" t="str">
+        <v>MHK1000-D001</v>
+      </c>
+      <c r="B992" t="str">
+        <v>MHK1000</v>
+      </c>
+      <c r="C992" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D992" t="str">
+        <v>G39808NP-BN-1/0-5U</v>
+      </c>
+      <c r="E992" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F992" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G992" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H992" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I992" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J992" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K992" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L992" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M992" t="str">
+        <v>The Mustad Grip-Pin® hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The 2X long shank hook is ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. The 2X strong wire hook is perfect fishing around heavy cover targeting a wide variety of species, such as big Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Strong 2X Long shank Straight shank Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N992" t="str">
+        <v/>
+      </c>
+      <c r="O992" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="str">
+        <v>MHK1000-D002</v>
+      </c>
+      <c r="B993" t="str">
+        <v>MHK1000</v>
+      </c>
+      <c r="C993" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D993" t="str">
+        <v>G39808NP-BN-2/0-5U</v>
+      </c>
+      <c r="E993" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F993" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G993" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H993" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I993" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J993" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K993" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L993" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M993" t="str">
+        <v>The Mustad Grip-Pin® hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The 2X long shank hook is ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. The 2X strong wire hook is perfect fishing around heavy cover targeting a wide variety of species, such as big Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Strong 2X Long shank Straight shank Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N993" t="str">
+        <v/>
+      </c>
+      <c r="O993" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v>MHK1000-D003</v>
+      </c>
+      <c r="B994" t="str">
+        <v>MHK1000</v>
+      </c>
+      <c r="C994" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D994" t="str">
+        <v>G39808NP-BN-3/0-5U</v>
+      </c>
+      <c r="E994" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F994" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G994" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H994" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I994" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J994" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K994" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L994" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M994" t="str">
+        <v>The Mustad Grip-Pin® hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The 2X long shank hook is ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. The 2X strong wire hook is perfect fishing around heavy cover targeting a wide variety of species, such as big Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Strong 2X Long shank Straight shank Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N994" t="str">
+        <v/>
+      </c>
+      <c r="O994" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v>MHK1000-D004</v>
+      </c>
+      <c r="B995" t="str">
+        <v>MHK1000</v>
+      </c>
+      <c r="C995" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D995" t="str">
+        <v>G39808NP-BN-4/0-5U</v>
+      </c>
+      <c r="E995" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F995" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G995" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H995" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I995" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J995" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K995" t="str">
+        <v>9.49</v>
+      </c>
+      <c r="L995" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M995" t="str">
+        <v>The Mustad Grip-Pin® hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The 2X long shank hook is ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. The 2X strong wire hook is perfect fishing around heavy cover targeting a wide variety of species, such as big Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Strong 2X Long shank Straight shank Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N995" t="str">
+        <v/>
+      </c>
+      <c r="O995" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v>MHK1000-D005</v>
+      </c>
+      <c r="B996" t="str">
+        <v>MHK1000</v>
+      </c>
+      <c r="C996" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D996" t="str">
+        <v>G39808NP-BN-5/0-5U</v>
+      </c>
+      <c r="E996" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F996" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G996" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H996" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I996" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J996" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K996" t="str">
+        <v>9.99</v>
+      </c>
+      <c r="L996" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M996" t="str">
+        <v>The Mustad Grip-Pin® hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The 2X long shank hook is ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. The 2X strong wire hook is perfect fishing around heavy cover targeting a wide variety of species, such as big Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Strong 2X Long shank Straight shank Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N996" t="str">
+        <v/>
+      </c>
+      <c r="O996" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v>MHK1000-D006</v>
+      </c>
+      <c r="B997" t="str">
+        <v>MHK1000</v>
+      </c>
+      <c r="C997" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D997" t="str">
+        <v>G39808NP-BN-6/0-5U</v>
+      </c>
+      <c r="E997" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F997" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G997" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H997" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I997" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J997" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K997" t="str">
+        <v>5.00</v>
+      </c>
+      <c r="L997" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M997" t="str">
+        <v>The Mustad Grip-Pin® hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The 2X long shank hook is ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. The 2X strong wire hook is perfect fishing around heavy cover targeting a wide variety of species, such as big Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Strong 2X Long shank Straight shank Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N997" t="str">
+        <v/>
+      </c>
+      <c r="O997" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="str">
+        <v>MHK1001-D001</v>
+      </c>
+      <c r="B998" t="str">
+        <v>MHK1001</v>
+      </c>
+      <c r="C998" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D998" t="str">
+        <v>10549NP-BN-4-10U</v>
+      </c>
+      <c r="E998" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F998" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G998" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H998" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I998" t="str">
+        <v>4</v>
+      </c>
+      <c r="J998" t="str">
+        <v/>
+      </c>
+      <c r="K998" t="str">
+        <v>3.49</v>
+      </c>
+      <c r="L998" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M998" t="str">
+        <v>This 1X fine wire hook for a delicate drop shot presentation when you nose hook the bait or as attached to tiny lures. Round bend wide gape for great hooking ability and presentation. Up-turned eye makes it perfect for the Snell knot and suspended presentation. This is truly a must-have hook for freshwater anglers, who expect the best from a hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N998" t="str">
+        <v/>
+      </c>
+      <c r="O998" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="str">
+        <v>MHK1001-D002</v>
+      </c>
+      <c r="B999" t="str">
+        <v>MHK1001</v>
+      </c>
+      <c r="C999" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D999" t="str">
+        <v>10549NP-BN-2-10U</v>
+      </c>
+      <c r="E999" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F999" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G999" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H999" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I999" t="str">
+        <v>2</v>
+      </c>
+      <c r="J999" t="str">
+        <v/>
+      </c>
+      <c r="K999" t="str">
+        <v>3.49</v>
+      </c>
+      <c r="L999" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M999" t="str">
+        <v>This 1X fine wire hook for a delicate drop shot presentation when you nose hook the bait or as attached to tiny lures. Round bend wide gape for great hooking ability and presentation. Up-turned eye makes it perfect for the Snell knot and suspended presentation. This is truly a must-have hook for freshwater anglers, who expect the best from a hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N999" t="str">
+        <v/>
+      </c>
+      <c r="O999" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="str">
+        <v>MHK1001-D003</v>
+      </c>
+      <c r="B1000" t="str">
+        <v>MHK1001</v>
+      </c>
+      <c r="C1000" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1000" t="str">
+        <v>10549NP-BN-1-10U</v>
+      </c>
+      <c r="E1000" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1000" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1000" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1000" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1000" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1000" t="str">
+        <v/>
+      </c>
+      <c r="K1000" t="str">
+        <v>3.49</v>
+      </c>
+      <c r="L1000" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1000" t="str">
+        <v>This 1X fine wire hook for a delicate drop shot presentation when you nose hook the bait or as attached to tiny lures. Round bend wide gape for great hooking ability and presentation. Up-turned eye makes it perfect for the Snell knot and suspended presentation. This is truly a must-have hook for freshwater anglers, who expect the best from a hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1000" t="str">
+        <v/>
+      </c>
+      <c r="O1000" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="str">
+        <v>MHK1001-D004</v>
+      </c>
+      <c r="B1001" t="str">
+        <v>MHK1001</v>
+      </c>
+      <c r="C1001" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1001" t="str">
+        <v>10549NP-BN-1/0-10U</v>
+      </c>
+      <c r="E1001" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1001" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1001" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1001" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1001" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1001" t="str">
+        <v/>
+      </c>
+      <c r="K1001" t="str">
+        <v>3.49</v>
+      </c>
+      <c r="L1001" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1001" t="str">
+        <v>This 1X fine wire hook for a delicate drop shot presentation when you nose hook the bait or as attached to tiny lures. Round bend wide gape for great hooking ability and presentation. Up-turned eye makes it perfect for the Snell knot and suspended presentation. This is truly a must-have hook for freshwater anglers, who expect the best from a hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1001" t="str">
+        <v/>
+      </c>
+      <c r="O1001" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="str">
+        <v>MHK1001-D005</v>
+      </c>
+      <c r="B1002" t="str">
+        <v>MHK1001</v>
+      </c>
+      <c r="C1002" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1002" t="str">
+        <v>10549NP-BN-2/0-10U</v>
+      </c>
+      <c r="E1002" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1002" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1002" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1002" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1002" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1002" t="str">
+        <v/>
+      </c>
+      <c r="K1002" t="str">
+        <v>3.49</v>
+      </c>
+      <c r="L1002" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1002" t="str">
+        <v>This 1X fine wire hook for a delicate drop shot presentation when you nose hook the bait or as attached to tiny lures. Round bend wide gape for great hooking ability and presentation. Up-turned eye makes it perfect for the Snell knot and suspended presentation. This is truly a must-have hook for freshwater anglers, who expect the best from a hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1002" t="str">
+        <v/>
+      </c>
+      <c r="O1002" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="str">
+        <v>MHK1001-D006</v>
+      </c>
+      <c r="B1003" t="str">
+        <v>MHK1001</v>
+      </c>
+      <c r="C1003" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1003" t="str">
+        <v>10549NP-BN-3/0-6U</v>
+      </c>
+      <c r="E1003" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1003" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1003" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1003" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1003" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1003" t="str">
+        <v/>
+      </c>
+      <c r="K1003" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1003" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1003" t="str">
+        <v>This 1X fine wire hook for a delicate drop shot presentation when you nose hook the bait or as attached to tiny lures. Round bend wide gape for great hooking ability and presentation. Up-turned eye makes it perfect for the Snell knot and suspended presentation. This is truly a must-have hook for freshwater anglers, who expect the best from a hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1003" t="str">
+        <v/>
+      </c>
+      <c r="O1003" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="str">
+        <v>MHK1002-D001</v>
+      </c>
+      <c r="B1004" t="str">
+        <v>MHK1002</v>
+      </c>
+      <c r="C1004" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1004" t="str">
+        <v>38101NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1004" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1004" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1004" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1004" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1004" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1004" t="str">
+        <v/>
+      </c>
+      <c r="K1004" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1004" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1004" t="str">
+        <v>The Grip-Pin® Soft Plastic fish hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. This extra wide bend bass fishing hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. Our Grip-Pinss are the best hooks for fishing Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which are 4 times as corrosion resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1004" t="str">
+        <v/>
+      </c>
+      <c r="O1004" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="str">
+        <v>MHK1002-D002</v>
+      </c>
+      <c r="B1005" t="str">
+        <v>MHK1002</v>
+      </c>
+      <c r="C1005" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1005" t="str">
+        <v>38101NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1005" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1005" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1005" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1005" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1005" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1005" t="str">
+        <v/>
+      </c>
+      <c r="K1005" t="str">
+        <v>9.49</v>
+      </c>
+      <c r="L1005" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1005" t="str">
+        <v>The Grip-Pin® Soft Plastic fish hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. This extra wide bend bass fishing hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. Our Grip-Pinss are the best hooks for fishing Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which are 4 times as corrosion resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1005" t="str">
+        <v/>
+      </c>
+      <c r="O1005" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="str">
+        <v>MHK1002-D003</v>
+      </c>
+      <c r="B1006" t="str">
+        <v>MHK1002</v>
+      </c>
+      <c r="C1006" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1006" t="str">
+        <v>38101NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1006" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1006" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1006" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1006" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1006" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1006" t="str">
+        <v/>
+      </c>
+      <c r="K1006" t="str">
+        <v>9.99</v>
+      </c>
+      <c r="L1006" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1006" t="str">
+        <v>The Grip-Pin® Soft Plastic fish hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. This extra wide bend bass fishing hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. Our Grip-Pinss are the best hooks for fishing Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which are 4 times as corrosion resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1006" t="str">
+        <v/>
+      </c>
+      <c r="O1006" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="str">
+        <v>MHK1002-D004</v>
+      </c>
+      <c r="B1007" t="str">
+        <v>MHK1002</v>
+      </c>
+      <c r="C1007" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1007" t="str">
+        <v>38101NP-BN-5/0-5U</v>
+      </c>
+      <c r="E1007" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1007" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1007" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1007" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1007" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1007" t="str">
+        <v/>
+      </c>
+      <c r="K1007" t="str">
+        <v>10.49</v>
+      </c>
+      <c r="L1007" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1007" t="str">
+        <v>The Grip-Pin® Soft Plastic fish hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. This extra wide bend bass fishing hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. Our Grip-Pinss are the best hooks for fishing Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which are 4 times as corrosion resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1007" t="str">
+        <v/>
+      </c>
+      <c r="O1007" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="str">
+        <v>MHK1002-D005</v>
+      </c>
+      <c r="B1008" t="str">
+        <v>MHK1002</v>
+      </c>
+      <c r="C1008" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1008" t="str">
+        <v>38101NP-BN-6/0-5U</v>
+      </c>
+      <c r="E1008" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1008" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1008" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1008" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1008" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1008" t="str">
+        <v/>
+      </c>
+      <c r="K1008" t="str">
+        <v>11.49</v>
+      </c>
+      <c r="L1008" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1008" t="str">
+        <v>The Grip-Pin® Soft Plastic fish hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. This extra wide bend bass fishing hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. Our Grip-Pinss are the best hooks for fishing Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which are 4 times as corrosion resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1008" t="str">
+        <v/>
+      </c>
+      <c r="O1008" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v>MHK1003-D001</v>
+      </c>
+      <c r="B1009" t="str">
+        <v>MHK1003</v>
+      </c>
+      <c r="C1009" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1009" t="str">
+        <v>G34042NP-BN-1/0-5U</v>
+      </c>
+      <c r="E1009" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1009" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1009" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1009" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1009" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1009" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1009" t="str">
+        <v>7.99</v>
+      </c>
+      <c r="L1009" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1009" t="str">
+        <v>The Mustad Grip-Pin® Edge Finesse Hook is designed for soft plastic swim baits, especially worms. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design, without tearing the bait. It is ideal for fishing weedless with perfect presentation and hooking properties. Fish it weightless or Texas or Drop Shot style to get at the deeper swimming fish. Use it for Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight Long shank Ringed eye Nor-Tempered PVC coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1009" t="str">
+        <v/>
+      </c>
+      <c r="O1009" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v>MHK1003-D002</v>
+      </c>
+      <c r="B1010" t="str">
+        <v>MHK1003</v>
+      </c>
+      <c r="C1010" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1010" t="str">
+        <v>G34042NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1010" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1010" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1010" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1010" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1010" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1010" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1010" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1010" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1010" t="str">
+        <v>The Mustad Grip-Pin® Edge Finesse Hook is designed for soft plastic swim baits, especially worms. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design, without tearing the bait. It is ideal for fishing weedless with perfect presentation and hooking properties. Fish it weightless or Texas or Drop Shot style to get at the deeper swimming fish. Use it for Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight Long shank Ringed eye Nor-Tempered PVC coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1010" t="str">
+        <v/>
+      </c>
+      <c r="O1010" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="str">
+        <v>MHK1003-D003</v>
+      </c>
+      <c r="B1011" t="str">
+        <v>MHK1003</v>
+      </c>
+      <c r="C1011" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1011" t="str">
+        <v>G34042NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1011" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1011" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1011" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1011" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1011" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1011" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1011" t="str">
+        <v>9.49</v>
+      </c>
+      <c r="L1011" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1011" t="str">
+        <v>The Mustad Grip-Pin® Edge Finesse Hook is designed for soft plastic swim baits, especially worms. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design, without tearing the bait. It is ideal for fishing weedless with perfect presentation and hooking properties. Fish it weightless or Texas or Drop Shot style to get at the deeper swimming fish. Use it for Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight Long shank Ringed eye Nor-Tempered PVC coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1011" t="str">
+        <v/>
+      </c>
+      <c r="O1011" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v>MHK1003-D004</v>
+      </c>
+      <c r="B1012" t="str">
+        <v>MHK1003</v>
+      </c>
+      <c r="C1012" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1012" t="str">
+        <v>G34042NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1012" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1012" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1012" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1012" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1012" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1012" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1012" t="str">
+        <v>9.99</v>
+      </c>
+      <c r="L1012" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1012" t="str">
+        <v>The Mustad Grip-Pin® Edge Finesse Hook is designed for soft plastic swim baits, especially worms. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design, without tearing the bait. It is ideal for fishing weedless with perfect presentation and hooking properties. Fish it weightless or Texas or Drop Shot style to get at the deeper swimming fish. Use it for Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight Long shank Ringed eye Nor-Tempered PVC coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1012" t="str">
+        <v/>
+      </c>
+      <c r="O1012" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v>MHK1003-D005</v>
+      </c>
+      <c r="B1013" t="str">
+        <v>MHK1003</v>
+      </c>
+      <c r="C1013" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1013" t="str">
+        <v>G34042NP-BN-5/0-5U</v>
+      </c>
+      <c r="E1013" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1013" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1013" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1013" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1013" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1013" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1013" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1013" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1013" t="str">
+        <v>The Mustad Grip-Pin® Edge Finesse Hook is designed for soft plastic swim baits, especially worms. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design, without tearing the bait. It is ideal for fishing weedless with perfect presentation and hooking properties. Fish it weightless or Texas or Drop Shot style to get at the deeper swimming fish. Use it for Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight Long shank Ringed eye Nor-Tempered PVC coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1013" t="str">
+        <v/>
+      </c>
+      <c r="O1013" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v>MHK1004-D001</v>
+      </c>
+      <c r="B1014" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1014" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1014" t="str">
+        <v>10548NP-RB-8-10U</v>
+      </c>
+      <c r="E1014" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1014" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1014" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1014" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1014" t="str">
+        <v>8</v>
+      </c>
+      <c r="J1014" t="str">
+        <v/>
+      </c>
+      <c r="K1014" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1014" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1014" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1014" t="str">
+        <v/>
+      </c>
+      <c r="O1014" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v>MHK1004-D002</v>
+      </c>
+      <c r="B1015" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1015" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1015" t="str">
+        <v>10548NP-RB-6-10U</v>
+      </c>
+      <c r="E1015" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1015" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1015" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1015" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1015" t="str">
+        <v>6</v>
+      </c>
+      <c r="J1015" t="str">
+        <v/>
+      </c>
+      <c r="K1015" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1015" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1015" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1015" t="str">
+        <v/>
+      </c>
+      <c r="O1015" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v>MHK1004-D003</v>
+      </c>
+      <c r="B1016" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1016" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1016" t="str">
+        <v>10548NP-BN-4-10U</v>
+      </c>
+      <c r="E1016" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1016" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1016" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1016" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1016" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1016" t="str">
+        <v/>
+      </c>
+      <c r="K1016" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1016" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1016" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1016" t="str">
+        <v/>
+      </c>
+      <c r="O1016" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v>MHK1004-D004</v>
+      </c>
+      <c r="B1017" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1017" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1017" t="str">
+        <v>10548NP-RB-4-10U</v>
+      </c>
+      <c r="E1017" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1017" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1017" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1017" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1017" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1017" t="str">
+        <v/>
+      </c>
+      <c r="K1017" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1017" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1017" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1017" t="str">
+        <v/>
+      </c>
+      <c r="O1017" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v>MHK1004-D005</v>
+      </c>
+      <c r="B1018" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1018" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1018" t="str">
+        <v>10548NP-BN-2-10U</v>
+      </c>
+      <c r="E1018" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1018" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1018" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1018" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1018" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1018" t="str">
+        <v/>
+      </c>
+      <c r="K1018" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1018" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1018" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1018" t="str">
+        <v/>
+      </c>
+      <c r="O1018" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v>MHK1004-D006</v>
+      </c>
+      <c r="B1019" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1019" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1019" t="str">
+        <v>10548NP-RB-2-10U</v>
+      </c>
+      <c r="E1019" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1019" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1019" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1019" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1019" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1019" t="str">
+        <v/>
+      </c>
+      <c r="K1019" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1019" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1019" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1019" t="str">
+        <v/>
+      </c>
+      <c r="O1019" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v>MHK1004-D007</v>
+      </c>
+      <c r="B1020" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1020" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1020" t="str">
+        <v>10548NP-BN-1-10U</v>
+      </c>
+      <c r="E1020" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1020" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1020" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1020" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1020" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1020" t="str">
+        <v/>
+      </c>
+      <c r="K1020" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1020" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1020" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1020" t="str">
+        <v/>
+      </c>
+      <c r="O1020" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v>MHK1004-D008</v>
+      </c>
+      <c r="B1021" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1021" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1021" t="str">
+        <v>10548NP-RB-1-10U</v>
+      </c>
+      <c r="E1021" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1021" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1021" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1021" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1021" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1021" t="str">
+        <v/>
+      </c>
+      <c r="K1021" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1021" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1021" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1021" t="str">
+        <v/>
+      </c>
+      <c r="O1021" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v>MHK1004-D009</v>
+      </c>
+      <c r="B1022" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1022" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1022" t="str">
+        <v>10548NP-BN-1/0-6U</v>
+      </c>
+      <c r="E1022" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1022" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1022" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1022" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1022" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1022" t="str">
+        <v/>
+      </c>
+      <c r="K1022" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1022" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1022" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1022" t="str">
+        <v/>
+      </c>
+      <c r="O1022" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v>MHK1004-D010</v>
+      </c>
+      <c r="B1023" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1023" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1023" t="str">
+        <v>10548NP-RB-1/0-6U</v>
+      </c>
+      <c r="E1023" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1023" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1023" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1023" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1023" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1023" t="str">
+        <v/>
+      </c>
+      <c r="K1023" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1023" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1023" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1023" t="str">
+        <v/>
+      </c>
+      <c r="O1023" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v>MHK1004-D011</v>
+      </c>
+      <c r="B1024" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1024" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1024" t="str">
+        <v>10548NP-BN-2/0-6U</v>
+      </c>
+      <c r="E1024" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1024" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1024" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1024" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1024" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1024" t="str">
+        <v/>
+      </c>
+      <c r="K1024" t="str">
+        <v>3.49</v>
+      </c>
+      <c r="L1024" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1024" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1024" t="str">
+        <v/>
+      </c>
+      <c r="O1024" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v>MHK1004-D012</v>
+      </c>
+      <c r="B1025" t="str">
+        <v>MHK1004</v>
+      </c>
+      <c r="C1025" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1025" t="str">
+        <v>10548NP-RB-2/0-5U</v>
+      </c>
+      <c r="E1025" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1025" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1025" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1025" t="str">
+        <v>Red Blonde / Black Nickel</v>
+      </c>
+      <c r="I1025" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1025" t="str">
+        <v/>
+      </c>
+      <c r="K1025" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1025" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1025" t="str">
+        <v>A dropshot rig is an efficient method for positioning your soft plastic lure near the bottom while avoiding snags. This wide gap Dropshot Hook ensures a gentle presentation of your bait, maximizing its appeal to fish while offering a wider gape that anglers find effective in many applications. Experiment with suspended or bouncing motions, incorporating spin stops for added allure. Secure your hook with the reliable Palomar knot, ensuring a precise 90-degree angle from the line. Target species like Bass, Perch, or Trout with this hook. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Forged Ringed eye Up Eye Nor-Tempered</v>
+      </c>
+      <c r="N1025" t="str">
+        <v/>
+      </c>
+      <c r="O1025" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v>MHK1005-D001</v>
+      </c>
+      <c r="B1026" t="str">
+        <v>MHK1005</v>
+      </c>
+      <c r="C1026" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1026" t="str">
+        <v>10546NP-BN-6-6U</v>
+      </c>
+      <c r="E1026" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1026" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1026" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1026" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1026" t="str">
+        <v>6</v>
+      </c>
+      <c r="J1026" t="str">
+        <v/>
+      </c>
+      <c r="K1026" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1026" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1026" t="str">
+        <v>Fishing the drop shot rig is an effective way to present your soft plastic lure close to the bottom, without snagging. The fine wire hook offers a delicate presentation of your lure. Fish it with a suspended presentation with a steady motion, or let it bounce off the bottom, leaving as many spin stops you like. Your soft plastic lure will be right in the striking zone. The best knot for tying the hook to the line is the Palomar knot, which will place it at a 90-degree angle from the line. Use it to target Bass, Perch or Trout in rivers, lakes or canals. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Up eye Nor-Tempered</v>
+      </c>
+      <c r="N1026" t="str">
+        <v/>
+      </c>
+      <c r="O1026" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v>MHK1005-D002</v>
+      </c>
+      <c r="B1027" t="str">
+        <v>MHK1005</v>
+      </c>
+      <c r="C1027" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1027" t="str">
+        <v>10546NP-RB-6-6U</v>
+      </c>
+      <c r="E1027" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1027" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1027" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1027" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1027" t="str">
+        <v>6</v>
+      </c>
+      <c r="J1027" t="str">
+        <v/>
+      </c>
+      <c r="K1027" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1027" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1027" t="str">
+        <v>Fishing the drop shot rig is an effective way to present your soft plastic lure close to the bottom, without snagging. The fine wire hook offers a delicate presentation of your lure. Fish it with a suspended presentation with a steady motion, or let it bounce off the bottom, leaving as many spin stops you like. Your soft plastic lure will be right in the striking zone. The best knot for tying the hook to the line is the Palomar knot, which will place it at a 90-degree angle from the line. Use it to target Bass, Perch or Trout in rivers, lakes or canals. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Up eye Nor-Tempered</v>
+      </c>
+      <c r="N1027" t="str">
+        <v/>
+      </c>
+      <c r="O1027" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v>MHK1005-D003</v>
+      </c>
+      <c r="B1028" t="str">
+        <v>MHK1005</v>
+      </c>
+      <c r="C1028" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1028" t="str">
+        <v>10546NP-BN-4-6U</v>
+      </c>
+      <c r="E1028" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1028" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1028" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1028" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1028" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1028" t="str">
+        <v/>
+      </c>
+      <c r="K1028" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1028" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1028" t="str">
+        <v>Fishing the drop shot rig is an effective way to present your soft plastic lure close to the bottom, without snagging. The fine wire hook offers a delicate presentation of your lure. Fish it with a suspended presentation with a steady motion, or let it bounce off the bottom, leaving as many spin stops you like. Your soft plastic lure will be right in the striking zone. The best knot for tying the hook to the line is the Palomar knot, which will place it at a 90-degree angle from the line. Use it to target Bass, Perch or Trout in rivers, lakes or canals. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Up eye Nor-Tempered</v>
+      </c>
+      <c r="N1028" t="str">
+        <v/>
+      </c>
+      <c r="O1028" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v>MHK1005-D004</v>
+      </c>
+      <c r="B1029" t="str">
+        <v>MHK1005</v>
+      </c>
+      <c r="C1029" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1029" t="str">
+        <v>10546NP-RB-4-6U</v>
+      </c>
+      <c r="E1029" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1029" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1029" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1029" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1029" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1029" t="str">
+        <v/>
+      </c>
+      <c r="K1029" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1029" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1029" t="str">
+        <v>Fishing the drop shot rig is an effective way to present your soft plastic lure close to the bottom, without snagging. The fine wire hook offers a delicate presentation of your lure. Fish it with a suspended presentation with a steady motion, or let it bounce off the bottom, leaving as many spin stops you like. Your soft plastic lure will be right in the striking zone. The best knot for tying the hook to the line is the Palomar knot, which will place it at a 90-degree angle from the line. Use it to target Bass, Perch or Trout in rivers, lakes or canals. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Up eye Nor-Tempered</v>
+      </c>
+      <c r="N1029" t="str">
+        <v/>
+      </c>
+      <c r="O1029" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v>MHK1005-D005</v>
+      </c>
+      <c r="B1030" t="str">
+        <v>MHK1005</v>
+      </c>
+      <c r="C1030" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1030" t="str">
+        <v>10546NP-BN-2-6U</v>
+      </c>
+      <c r="E1030" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1030" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1030" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1030" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1030" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1030" t="str">
+        <v/>
+      </c>
+      <c r="K1030" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1030" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1030" t="str">
+        <v>Fishing the drop shot rig is an effective way to present your soft plastic lure close to the bottom, without snagging. The fine wire hook offers a delicate presentation of your lure. Fish it with a suspended presentation with a steady motion, or let it bounce off the bottom, leaving as many spin stops you like. Your soft plastic lure will be right in the striking zone. The best knot for tying the hook to the line is the Palomar knot, which will place it at a 90-degree angle from the line. Use it to target Bass, Perch or Trout in rivers, lakes or canals. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Up eye Nor-Tempered</v>
+      </c>
+      <c r="N1030" t="str">
+        <v/>
+      </c>
+      <c r="O1030" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="str">
+        <v>MHK1005-D006</v>
+      </c>
+      <c r="B1031" t="str">
+        <v>MHK1005</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1031" t="str">
+        <v>10546NP-RB-2-6U</v>
+      </c>
+      <c r="E1031" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1031" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1031" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1031" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1031" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1031" t="str">
+        <v/>
+      </c>
+      <c r="K1031" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1031" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1031" t="str">
+        <v>Fishing the drop shot rig is an effective way to present your soft plastic lure close to the bottom, without snagging. The fine wire hook offers a delicate presentation of your lure. Fish it with a suspended presentation with a steady motion, or let it bounce off the bottom, leaving as many spin stops you like. Your soft plastic lure will be right in the striking zone. The best knot for tying the hook to the line is the Palomar knot, which will place it at a 90-degree angle from the line. Use it to target Bass, Perch or Trout in rivers, lakes or canals. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Up eye Nor-Tempered</v>
+      </c>
+      <c r="N1031" t="str">
+        <v/>
+      </c>
+      <c r="O1031" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v>MHK1006-D001</v>
+      </c>
+      <c r="B1032" t="str">
+        <v>MHK1006</v>
+      </c>
+      <c r="C1032" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1032" t="str">
+        <v>60403NP-TX-4-6U</v>
+      </c>
+      <c r="E1032" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1032" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1032" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1032" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1032" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1032" t="str">
+        <v/>
+      </c>
+      <c r="K1032" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1032" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1032" t="str">
+        <v>The TitanX Wacky/Neko Hook features a non-reflective, natural look that won't spook the fish in clear conditions, but provide 4 times better penetration as well. Made for multiple techniques such as Wacky, Neko or Drop shot rigging. “They are the best drop shot/wacky rig hooks I have ever used” - says Mustad Pro Staff Kevin VanDam - and he has the tournament wins to prove it. Perfect for using with a great variety of soft plastic worms, targeting deeper lying fish around structures, drop-offs or ledges. This technique has a great variety of applications in both fresh and saltwater, targeting Largemouth or Smallmouth Bass, Northern Pike, Muskie, Perch, Zander, Walleye, Brown Trout, Redfish, Speckled Sea Trout, Snook, Redfish, Striped Bass, Cod or Dorado/Mahi Mahi. The TitanX Wacky/Neko hook has also become popular among saltwater fly fishermen when tying crab imitations targeting Redfish, Bonefish, Black Drum and Sea Trout. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Long Sproat bend Wide Gap Ringed eye TitanX finish</v>
+      </c>
+      <c r="N1032" t="str">
+        <v/>
+      </c>
+      <c r="O1032" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="str">
+        <v>MHK1006-D002</v>
+      </c>
+      <c r="B1033" t="str">
+        <v>MHK1006</v>
+      </c>
+      <c r="C1033" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1033" t="str">
+        <v>60403NP-TX-2-6U</v>
+      </c>
+      <c r="E1033" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1033" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1033" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1033" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1033" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1033" t="str">
+        <v/>
+      </c>
+      <c r="K1033" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1033" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1033" t="str">
+        <v>The TitanX Wacky/Neko Hook features a non-reflective, natural look that won't spook the fish in clear conditions, but provide 4 times better penetration as well. Made for multiple techniques such as Wacky, Neko or Drop shot rigging. “They are the best drop shot/wacky rig hooks I have ever used” - says Mustad Pro Staff Kevin VanDam - and he has the tournament wins to prove it. Perfect for using with a great variety of soft plastic worms, targeting deeper lying fish around structures, drop-offs or ledges. This technique has a great variety of applications in both fresh and saltwater, targeting Largemouth or Smallmouth Bass, Northern Pike, Muskie, Perch, Zander, Walleye, Brown Trout, Redfish, Speckled Sea Trout, Snook, Redfish, Striped Bass, Cod or Dorado/Mahi Mahi. The TitanX Wacky/Neko hook has also become popular among saltwater fly fishermen when tying crab imitations targeting Redfish, Bonefish, Black Drum and Sea Trout. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Long Sproat bend Wide Gap Ringed eye TitanX finish</v>
+      </c>
+      <c r="N1033" t="str">
+        <v/>
+      </c>
+      <c r="O1033" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="str">
+        <v>MHK1006-D003</v>
+      </c>
+      <c r="B1034" t="str">
+        <v>MHK1006</v>
+      </c>
+      <c r="C1034" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1034" t="str">
+        <v>60403NP-TX-1-6U</v>
+      </c>
+      <c r="E1034" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1034" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1034" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1034" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1034" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1034" t="str">
+        <v/>
+      </c>
+      <c r="K1034" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1034" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1034" t="str">
+        <v>The TitanX Wacky/Neko Hook features a non-reflective, natural look that won't spook the fish in clear conditions, but provide 4 times better penetration as well. Made for multiple techniques such as Wacky, Neko or Drop shot rigging. “They are the best drop shot/wacky rig hooks I have ever used” - says Mustad Pro Staff Kevin VanDam - and he has the tournament wins to prove it. Perfect for using with a great variety of soft plastic worms, targeting deeper lying fish around structures, drop-offs or ledges. This technique has a great variety of applications in both fresh and saltwater, targeting Largemouth or Smallmouth Bass, Northern Pike, Muskie, Perch, Zander, Walleye, Brown Trout, Redfish, Speckled Sea Trout, Snook, Redfish, Striped Bass, Cod or Dorado/Mahi Mahi. The TitanX Wacky/Neko hook has also become popular among saltwater fly fishermen when tying crab imitations targeting Redfish, Bonefish, Black Drum and Sea Trout. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Long Sproat bend Wide Gap Ringed eye TitanX finish</v>
+      </c>
+      <c r="N1034" t="str">
+        <v/>
+      </c>
+      <c r="O1034" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="str">
+        <v>MHK1006-D004</v>
+      </c>
+      <c r="B1035" t="str">
+        <v>MHK1006</v>
+      </c>
+      <c r="C1035" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1035" t="str">
+        <v>60403NP-TX-1/0-6U</v>
+      </c>
+      <c r="E1035" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1035" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1035" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1035" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1035" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1035" t="str">
+        <v/>
+      </c>
+      <c r="K1035" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1035" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1035" t="str">
+        <v>The TitanX Wacky/Neko Hook features a non-reflective, natural look that won't spook the fish in clear conditions, but provide 4 times better penetration as well. Made for multiple techniques such as Wacky, Neko or Drop shot rigging. “They are the best drop shot/wacky rig hooks I have ever used” - says Mustad Pro Staff Kevin VanDam - and he has the tournament wins to prove it. Perfect for using with a great variety of soft plastic worms, targeting deeper lying fish around structures, drop-offs or ledges. This technique has a great variety of applications in both fresh and saltwater, targeting Largemouth or Smallmouth Bass, Northern Pike, Muskie, Perch, Zander, Walleye, Brown Trout, Redfish, Speckled Sea Trout, Snook, Redfish, Striped Bass, Cod or Dorado/Mahi Mahi. The TitanX Wacky/Neko hook has also become popular among saltwater fly fishermen when tying crab imitations targeting Redfish, Bonefish, Black Drum and Sea Trout. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Long Sproat bend Wide Gap Ringed eye TitanX finish</v>
+      </c>
+      <c r="N1035" t="str">
+        <v/>
+      </c>
+      <c r="O1035" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="str">
+        <v>MHK1006-D005</v>
+      </c>
+      <c r="B1036" t="str">
+        <v>MHK1006</v>
+      </c>
+      <c r="C1036" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1036" t="str">
+        <v>60403NP-TX-2/0-6U</v>
+      </c>
+      <c r="E1036" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1036" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1036" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1036" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1036" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1036" t="str">
+        <v/>
+      </c>
+      <c r="K1036" t="str">
+        <v>3.99</v>
+      </c>
+      <c r="L1036" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1036" t="str">
+        <v>The TitanX Wacky/Neko Hook features a non-reflective, natural look that won't spook the fish in clear conditions, but provide 4 times better penetration as well. Made for multiple techniques such as Wacky, Neko or Drop shot rigging. “They are the best drop shot/wacky rig hooks I have ever used” - says Mustad Pro Staff Kevin VanDam - and he has the tournament wins to prove it. Perfect for using with a great variety of soft plastic worms, targeting deeper lying fish around structures, drop-offs or ledges. This technique has a great variety of applications in both fresh and saltwater, targeting Largemouth or Smallmouth Bass, Northern Pike, Muskie, Perch, Zander, Walleye, Brown Trout, Redfish, Speckled Sea Trout, Snook, Redfish, Striped Bass, Cod or Dorado/Mahi Mahi. The TitanX Wacky/Neko hook has also become popular among saltwater fly fishermen when tying crab imitations targeting Redfish, Bonefish, Black Drum and Sea Trout. 4.3 UltraPoint® Technology Opti-Angle Needle Point 2X Long Sproat bend Wide Gap Ringed eye TitanX finish</v>
+      </c>
+      <c r="N1036" t="str">
+        <v/>
+      </c>
+      <c r="O1036" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="str">
+        <v>MHK1007-D001</v>
+      </c>
+      <c r="B1037" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1037" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1037" t="str">
+        <v>37177NP-BN-2-25U</v>
+      </c>
+      <c r="E1037" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1037" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1037" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1037" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1037" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1037" t="str">
+        <v/>
+      </c>
+      <c r="K1037" t="str">
+        <v>9.75</v>
+      </c>
+      <c r="L1037" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1037" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1037" t="str">
+        <v/>
+      </c>
+      <c r="O1037" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="str">
+        <v>MHK1007-D002</v>
+      </c>
+      <c r="B1038" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1038" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1038" t="str">
+        <v>37177NP-BN-1/0-5U</v>
+      </c>
+      <c r="E1038" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1038" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1038" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1038" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1038" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1038" t="str">
+        <v/>
+      </c>
+      <c r="K1038" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1038" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1038" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1038" t="str">
+        <v/>
+      </c>
+      <c r="O1038" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="str">
+        <v>MHK1007-D003</v>
+      </c>
+      <c r="B1039" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1039" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1039" t="str">
+        <v>37177NP-BN-1/0-25U</v>
+      </c>
+      <c r="E1039" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1039" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1039" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1039" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1039" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1039" t="str">
+        <v/>
+      </c>
+      <c r="K1039" t="str">
+        <v>9.75</v>
+      </c>
+      <c r="L1039" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1039" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1039" t="str">
+        <v/>
+      </c>
+      <c r="O1039" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="str">
+        <v>MHK1007-D004</v>
+      </c>
+      <c r="B1040" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1040" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1040" t="str">
+        <v>37177NP-RB-1/0-25U</v>
+      </c>
+      <c r="E1040" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1040" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1040" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1040" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1040" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1040" t="str">
+        <v/>
+      </c>
+      <c r="K1040" t="str">
+        <v>17.99</v>
+      </c>
+      <c r="L1040" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1040" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1040" t="str">
+        <v/>
+      </c>
+      <c r="O1040" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="str">
+        <v>MHK1007-D005</v>
+      </c>
+      <c r="B1041" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1041" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1041" t="str">
+        <v>37177NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1041" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1041" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1041" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1041" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1041" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1041" t="str">
+        <v/>
+      </c>
+      <c r="K1041" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1041" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1041" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1041" t="str">
+        <v/>
+      </c>
+      <c r="O1041" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="str">
+        <v>MHK1007-D006</v>
+      </c>
+      <c r="B1042" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1042" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1042" t="str">
+        <v>37177NP-BN-2/0-25U</v>
+      </c>
+      <c r="E1042" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1042" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1042" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1042" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1042" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1042" t="str">
+        <v/>
+      </c>
+      <c r="K1042" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1042" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1042" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1042" t="str">
+        <v/>
+      </c>
+      <c r="O1042" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="str">
+        <v>MHK1007-D007</v>
+      </c>
+      <c r="B1043" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1043" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1043" t="str">
+        <v>37177NP-RB-2/0-25U</v>
+      </c>
+      <c r="E1043" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1043" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1043" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1043" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1043" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1043" t="str">
+        <v/>
+      </c>
+      <c r="K1043" t="str">
+        <v>17.99</v>
+      </c>
+      <c r="L1043" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1043" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1043" t="str">
+        <v/>
+      </c>
+      <c r="O1043" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="str">
+        <v>MHK1007-D008</v>
+      </c>
+      <c r="B1044" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1044" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1044" t="str">
+        <v>37177NP-RB-3/0-25U</v>
+      </c>
+      <c r="E1044" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1044" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1044" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1044" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1044" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1044" t="str">
+        <v/>
+      </c>
+      <c r="K1044" t="str">
+        <v>17.99</v>
+      </c>
+      <c r="L1044" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1044" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1044" t="str">
+        <v/>
+      </c>
+      <c r="O1044" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="str">
+        <v>MHK1007-D009</v>
+      </c>
+      <c r="B1045" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1045" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1045" t="str">
+        <v>37177NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1045" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1045" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1045" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1045" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1045" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1045" t="str">
+        <v/>
+      </c>
+      <c r="K1045" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1045" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1045" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1045" t="str">
+        <v/>
+      </c>
+      <c r="O1045" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="str">
+        <v>MHK1007-D010</v>
+      </c>
+      <c r="B1046" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1046" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1046" t="str">
+        <v>37177NP-BN-3/0-25U</v>
+      </c>
+      <c r="E1046" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1046" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1046" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1046" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1046" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1046" t="str">
+        <v/>
+      </c>
+      <c r="K1046" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1046" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1046" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1046" t="str">
+        <v/>
+      </c>
+      <c r="O1046" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="str">
+        <v>MHK1007-D011</v>
+      </c>
+      <c r="B1047" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1047" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1047" t="str">
+        <v>37177NP-RB-4/0-25U</v>
+      </c>
+      <c r="E1047" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1047" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1047" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1047" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1047" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1047" t="str">
+        <v/>
+      </c>
+      <c r="K1047" t="str">
+        <v>17.99</v>
+      </c>
+      <c r="L1047" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1047" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1047" t="str">
+        <v/>
+      </c>
+      <c r="O1047" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="str">
+        <v>MHK1007-D012</v>
+      </c>
+      <c r="B1048" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1048" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1048" t="str">
+        <v>37177NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1048" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1048" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1048" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1048" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1048" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1048" t="str">
+        <v/>
+      </c>
+      <c r="K1048" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1048" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1048" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1048" t="str">
+        <v/>
+      </c>
+      <c r="O1048" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="str">
+        <v>MHK1007-D013</v>
+      </c>
+      <c r="B1049" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1049" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1049" t="str">
+        <v>37177NP-BN-4/0-25U</v>
+      </c>
+      <c r="E1049" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1049" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1049" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1049" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1049" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1049" t="str">
+        <v/>
+      </c>
+      <c r="K1049" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1049" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1049" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1049" t="str">
+        <v/>
+      </c>
+      <c r="O1049" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="str">
+        <v>MHK1007-D014</v>
+      </c>
+      <c r="B1050" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1050" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1050" t="str">
+        <v>37177NP-BN-5/0-5U</v>
+      </c>
+      <c r="E1050" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1050" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1050" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1050" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1050" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1050" t="str">
+        <v/>
+      </c>
+      <c r="K1050" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1050" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1050" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1050" t="str">
+        <v/>
+      </c>
+      <c r="O1050" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="str">
+        <v>MHK1007-D015</v>
+      </c>
+      <c r="B1051" t="str">
+        <v>MHK1007</v>
+      </c>
+      <c r="C1051" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1051" t="str">
+        <v>37177NP-BN-5/0-25U</v>
+      </c>
+      <c r="E1051" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1051" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1051" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1051" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1051" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1051" t="str">
+        <v/>
+      </c>
+      <c r="K1051" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1051" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1051" t="str">
+        <v>The Mega Bite® Worm Offset Shank fish Hook is designed for soft large plastic worms. It is a perfect setup for free water fishing with the hook exposed. The wide gap and extra wide bend leaves room for more bulky soft plastic worms. Fish it Texas or Carolina rig style or just free swimming. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1051" t="str">
+        <v/>
+      </c>
+      <c r="O1051" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v>MHK1008-D001</v>
+      </c>
+      <c r="B1052" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1052" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1052" t="str">
+        <v>38104NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1052" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1052" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1052" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1052" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1052" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1052" t="str">
+        <v/>
+      </c>
+      <c r="K1052" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1052" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1052" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1052" t="str">
+        <v/>
+      </c>
+      <c r="O1052" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v>MHK1008-D002</v>
+      </c>
+      <c r="B1053" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1053" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1053" t="str">
+        <v>38104NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1053" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1053" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1053" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1053" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1053" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1053" t="str">
+        <v/>
+      </c>
+      <c r="K1053" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1053" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1053" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1053" t="str">
+        <v/>
+      </c>
+      <c r="O1053" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v>MHK1008-D003</v>
+      </c>
+      <c r="B1054" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1054" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1054" t="str">
+        <v>38104NP-BN-3/0-1000</v>
+      </c>
+      <c r="E1054" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1054" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1054" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1054" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1054" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1054" t="str">
+        <v/>
+      </c>
+      <c r="K1054" t="str">
+        <v>314.99</v>
+      </c>
+      <c r="L1054" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1054" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1054" t="str">
+        <v/>
+      </c>
+      <c r="O1054" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="str">
+        <v>MHK1008-D004</v>
+      </c>
+      <c r="B1055" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1055" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1055" t="str">
+        <v>38104NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1055" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1055" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1055" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1055" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1055" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1055" t="str">
+        <v/>
+      </c>
+      <c r="K1055" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1055" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1055" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1055" t="str">
+        <v/>
+      </c>
+      <c r="O1055" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v>MHK1008-D005</v>
+      </c>
+      <c r="B1056" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1056" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1056" t="str">
+        <v>38104NP-BN-4/0-1000</v>
+      </c>
+      <c r="E1056" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1056" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1056" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1056" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1056" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1056" t="str">
+        <v/>
+      </c>
+      <c r="K1056" t="str">
+        <v>314.99</v>
+      </c>
+      <c r="L1056" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1056" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1056" t="str">
+        <v/>
+      </c>
+      <c r="O1056" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="str">
+        <v>MHK1008-D006</v>
+      </c>
+      <c r="B1057" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1057" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1057" t="str">
+        <v>38104NP-BN-5/0-5U</v>
+      </c>
+      <c r="E1057" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1057" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1057" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1057" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1057" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1057" t="str">
+        <v/>
+      </c>
+      <c r="K1057" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1057" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1057" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1057" t="str">
+        <v/>
+      </c>
+      <c r="O1057" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="str">
+        <v>MHK1008-D007</v>
+      </c>
+      <c r="B1058" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1058" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1058" t="str">
+        <v>38104NP-BN-5/0-1000</v>
+      </c>
+      <c r="E1058" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1058" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1058" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1058" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1058" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1058" t="str">
+        <v/>
+      </c>
+      <c r="K1058" t="str">
+        <v>349.99</v>
+      </c>
+      <c r="L1058" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1058" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1058" t="str">
+        <v/>
+      </c>
+      <c r="O1058" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="str">
+        <v>MHK1008-D008</v>
+      </c>
+      <c r="B1059" t="str">
+        <v>MHK1008</v>
+      </c>
+      <c r="C1059" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1059" t="str">
+        <v>38104NP-BN-6/0-5U</v>
+      </c>
+      <c r="E1059" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1059" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1059" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1059" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1059" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1059" t="str">
+        <v/>
+      </c>
+      <c r="K1059" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1059" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1059" t="str">
+        <v>Crush big freshwater predators with Mustad's Big Mouth hooks paired with your favorite large soft plastic worms. Bulky baits present perfectly thanks to the wide gap and extra wide bend. Anglers often fish this freely with the hook exposed, or in Texas or Carolina rigs. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Strong Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1059" t="str">
+        <v/>
+      </c>
+      <c r="O1059" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v>MHK1009-D001</v>
+      </c>
+      <c r="B1060" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1060" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1060" t="str">
+        <v>38101W14-6/0-3U</v>
+      </c>
+      <c r="E1060" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1060" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1060" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1060" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1060" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1060" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1060" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1060" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1060" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1060" t="str">
+        <v/>
+      </c>
+      <c r="O1060" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="str">
+        <v>MHK1009-D002</v>
+      </c>
+      <c r="B1061" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1061" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1061" t="str">
+        <v>38101W14-5/0-3U</v>
+      </c>
+      <c r="E1061" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1061" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1061" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1061" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1061" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1061" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1061" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1061" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1061" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1061" t="str">
+        <v/>
+      </c>
+      <c r="O1061" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v>MHK1009-D003</v>
+      </c>
+      <c r="B1062" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1062" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1062" t="str">
+        <v>38101W18-6/0-3U</v>
+      </c>
+      <c r="E1062" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1062" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1062" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1062" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1062" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1062" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1062" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1062" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1062" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1062" t="str">
+        <v/>
+      </c>
+      <c r="O1062" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v>MHK1009-D004</v>
+      </c>
+      <c r="B1063" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1063" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1063" t="str">
+        <v>38101W18-5/0-3U</v>
+      </c>
+      <c r="E1063" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1063" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1063" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1063" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1063" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1063" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1063" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1063" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1063" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1063" t="str">
+        <v/>
+      </c>
+      <c r="O1063" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v>MHK1009-D005</v>
+      </c>
+      <c r="B1064" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1064" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1064" t="str">
+        <v>38101W18-4/0-3U</v>
+      </c>
+      <c r="E1064" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1064" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1064" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1064" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1064" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1064" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1064" t="str">
+        <v>7.49</v>
+      </c>
+      <c r="L1064" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1064" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1064" t="str">
+        <v/>
+      </c>
+      <c r="O1064" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v>MHK1009-D006</v>
+      </c>
+      <c r="B1065" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1065" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1065" t="str">
+        <v>38101W18-3/0-3U</v>
+      </c>
+      <c r="E1065" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1065" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1065" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1065" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1065" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1065" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1065" t="str">
+        <v>7.99</v>
+      </c>
+      <c r="L1065" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1065" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1065" t="str">
+        <v/>
+      </c>
+      <c r="O1065" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v>MHK1009-D007</v>
+      </c>
+      <c r="B1066" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1066" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1066" t="str">
+        <v>38101W116-5/0-3U</v>
+      </c>
+      <c r="E1066" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1066" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1066" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1066" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1066" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1066" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1066" t="str">
+        <v>7.99</v>
+      </c>
+      <c r="L1066" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1066" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1066" t="str">
+        <v/>
+      </c>
+      <c r="O1066" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v>MHK1009-D008</v>
+      </c>
+      <c r="B1067" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1067" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1067" t="str">
+        <v>38101W116-4/0-3U</v>
+      </c>
+      <c r="E1067" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1067" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1067" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1067" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1067" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1067" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1067" t="str">
+        <v>7.49</v>
+      </c>
+      <c r="L1067" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1067" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1067" t="str">
+        <v/>
+      </c>
+      <c r="O1067" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v>MHK1009-D009</v>
+      </c>
+      <c r="B1068" t="str">
+        <v>MHK1009</v>
+      </c>
+      <c r="C1068" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1068" t="str">
+        <v>38101W116-3/0-3U</v>
+      </c>
+      <c r="E1068" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1068" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1068" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1068" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1068" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1068" t="str">
+        <v>3U</v>
+      </c>
+      <c r="K1068" t="str">
+        <v>7.49</v>
+      </c>
+      <c r="L1068" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1068" t="str">
+        <v>The Weighted Grip Pin® Hook features a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the bait. Expanding upon Mustad’s popular Grip-Pin series, the Mustad Weighted KVD Grip Pin Hook features a sleek integrated 1/8oz/3,54g perfectly balanced belly weight, which allows anglers to effectively fish deeper waters. The 1X strong wire makes a great platform for fishing near hard cover and vegetation. The hook is designed for a big range of soft plastic lures such as shads, worms or swim baits. Use it to catch Bass, Perch, Zander, Brown Trout, Rainbow Trout, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Strong Extra wide bend Ringed eye Forged Nor-Tempered 1/8oz/3,54g weighted hook Resin-coated Grip Pin® Black Nickel finish</v>
+      </c>
+      <c r="N1068" t="str">
+        <v/>
+      </c>
+      <c r="O1068" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="str">
+        <v>MHK1010-D001</v>
+      </c>
+      <c r="B1069" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1069" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1069" t="str">
+        <v>91768S14-6/0-3U</v>
+      </c>
+      <c r="E1069" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1069" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1069" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1069" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1069" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1069" t="str">
+        <v/>
+      </c>
+      <c r="K1069" t="str">
+        <v>9.99</v>
+      </c>
+      <c r="L1069" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1069" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1069" t="str">
+        <v/>
+      </c>
+      <c r="O1069" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v>MHK1010-D002</v>
+      </c>
+      <c r="B1070" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1070" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1070" t="str">
+        <v>91768S18-5/0-3U</v>
+      </c>
+      <c r="E1070" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1070" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1070" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1070" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1070" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1070" t="str">
+        <v/>
+      </c>
+      <c r="K1070" t="str">
+        <v>3.75</v>
+      </c>
+      <c r="L1070" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1070" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1070" t="str">
+        <v/>
+      </c>
+      <c r="O1070" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="str">
+        <v>MHK1010-D003</v>
+      </c>
+      <c r="B1071" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1071" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1071" t="str">
+        <v>91768S18-4/0-3U</v>
+      </c>
+      <c r="E1071" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1071" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1071" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1071" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1071" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1071" t="str">
+        <v/>
+      </c>
+      <c r="K1071" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1071" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1071" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1071" t="str">
+        <v/>
+      </c>
+      <c r="O1071" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v>MHK1010-D004</v>
+      </c>
+      <c r="B1072" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1072" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1072" t="str">
+        <v>91768S18-3/0-3U</v>
+      </c>
+      <c r="E1072" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1072" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1072" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1072" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1072" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1072" t="str">
+        <v/>
+      </c>
+      <c r="K1072" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1072" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1072" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1072" t="str">
+        <v/>
+      </c>
+      <c r="O1072" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v>MHK1010-D005</v>
+      </c>
+      <c r="B1073" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1073" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1073" t="str">
+        <v>91768S18-2/0-3U</v>
+      </c>
+      <c r="E1073" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1073" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1073" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1073" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1073" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1073" t="str">
+        <v/>
+      </c>
+      <c r="K1073" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1073" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1073" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1073" t="str">
+        <v/>
+      </c>
+      <c r="O1073" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v>MHK1010-D006</v>
+      </c>
+      <c r="B1074" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1074" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1074" t="str">
+        <v>91768S18-1/0-3U</v>
+      </c>
+      <c r="E1074" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1074" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1074" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1074" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1074" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1074" t="str">
+        <v/>
+      </c>
+      <c r="K1074" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1074" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1074" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1074" t="str">
+        <v/>
+      </c>
+      <c r="O1074" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v>MHK1010-D007</v>
+      </c>
+      <c r="B1075" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1075" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1075" t="str">
+        <v>91768S116-5/0-3U</v>
+      </c>
+      <c r="E1075" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1075" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1075" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1075" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1075" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1075" t="str">
+        <v/>
+      </c>
+      <c r="K1075" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1075" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1075" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1075" t="str">
+        <v/>
+      </c>
+      <c r="O1075" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v>MHK1010-D008</v>
+      </c>
+      <c r="B1076" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1076" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1076" t="str">
+        <v>91768S116-4/0-3U</v>
+      </c>
+      <c r="E1076" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1076" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1076" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1076" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1076" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1076" t="str">
+        <v/>
+      </c>
+      <c r="K1076" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1076" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1076" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1076" t="str">
+        <v/>
+      </c>
+      <c r="O1076" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v>MHK1010-D009</v>
+      </c>
+      <c r="B1077" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>91768S116-3/0-3U</v>
+      </c>
+      <c r="E1077" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1077" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1077" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1077" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1077" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1077" t="str">
+        <v/>
+      </c>
+      <c r="K1077" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1077" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1077" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1077" t="str">
+        <v/>
+      </c>
+      <c r="O1077" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v>MHK1010-D010</v>
+      </c>
+      <c r="B1078" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1078" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1078" t="str">
+        <v>91768S116-2/0-3U</v>
+      </c>
+      <c r="E1078" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1078" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1078" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1078" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1078" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1078" t="str">
+        <v/>
+      </c>
+      <c r="K1078" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1078" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1078" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1078" t="str">
+        <v/>
+      </c>
+      <c r="O1078" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v>MHK1010-D011</v>
+      </c>
+      <c r="B1079" t="str">
+        <v>MHK1010</v>
+      </c>
+      <c r="C1079" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1079" t="str">
+        <v>91768S116-1/0-3U</v>
+      </c>
+      <c r="E1079" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1079" t="str">
+        <v>Swimbait Hook</v>
+      </c>
+      <c r="G1079" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1079" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1079" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1079" t="str">
+        <v/>
+      </c>
+      <c r="K1079" t="str">
+        <v>8.49</v>
+      </c>
+      <c r="L1079" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1079" t="str">
+        <v>The Power Lock Plus Spring Keeper Hook features a tapered spring gripper, offering a secure hold for your favorite swimbait with as much as 80% more grip strength. The unique adjustable sliding, build-in weight allows for back, forward or centered presentation. Moving the weight is easy. Rotate the weight several times to heat silicon insert. Move weight to desired position. As the insert cools, the weight will be held firmly in place again. Back position will push the bait backwards under structures like logs and docks. Use with tube baits, crawfish or jerkbaits. Forward position will make the bait dive nose down. Centered position will make the bait sink horizontally. The wide gap provides excellent hooking and holding abilities for big fish. Use it for Bass, Perch, Zander, Pike or Walleye.</v>
+      </c>
+      <c r="N1079" t="str">
+        <v/>
+      </c>
+      <c r="O1079" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v>MHK1011-D001</v>
+      </c>
+      <c r="B1080" t="str">
+        <v>MHK1011</v>
+      </c>
+      <c r="C1080" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1080" t="str">
+        <v>W37754-RB-1/0-5U</v>
+      </c>
+      <c r="E1080" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1080" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1080" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1080" t="str">
+        <v>Red Blonde</v>
+      </c>
+      <c r="I1080" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1080" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1080" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1080" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1080" t="str">
+        <v>The Mustad KVD Wacky Worm Hook is the perfect wide gap heavy cover hook targeting everything from big Bass and Redfish along with many other strong saltwater species. Perfect for tube bait soft lures. Fish it Wacky or Dropshot style. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Comes in Blonde Red finish. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Nor-Tempered Blonde red finish</v>
+      </c>
+      <c r="N1080" t="str">
+        <v/>
+      </c>
+      <c r="O1080" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="str">
+        <v>MHK1011-D002</v>
+      </c>
+      <c r="B1081" t="str">
+        <v>MHK1011</v>
+      </c>
+      <c r="C1081" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1081" t="str">
+        <v>W37754-RB-2/0-5U</v>
+      </c>
+      <c r="E1081" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1081" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1081" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1081" t="str">
+        <v>Red Blonde</v>
+      </c>
+      <c r="I1081" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1081" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1081" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1081" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1081" t="str">
+        <v>The Mustad KVD Wacky Worm Hook is the perfect wide gap heavy cover hook targeting everything from big Bass and Redfish along with many other strong saltwater species. Perfect for tube bait soft lures. Fish it Wacky or Dropshot style. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Comes in Blonde Red finish. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Nor-Tempered Blonde red finish</v>
+      </c>
+      <c r="N1081" t="str">
+        <v/>
+      </c>
+      <c r="O1081" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v>MHK1011-D003</v>
+      </c>
+      <c r="B1082" t="str">
+        <v>MHK1011</v>
+      </c>
+      <c r="C1082" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1082" t="str">
+        <v>W37754-RB-3/0-4U</v>
+      </c>
+      <c r="E1082" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1082" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1082" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1082" t="str">
+        <v>Red Blonde</v>
+      </c>
+      <c r="I1082" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1082" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1082" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1082" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1082" t="str">
+        <v>The Mustad KVD Wacky Worm Hook is the perfect wide gap heavy cover hook targeting everything from big Bass and Redfish along with many other strong saltwater species. Perfect for tube bait soft lures. Fish it Wacky or Dropshot style. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Comes in Blonde Red finish. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Nor-Tempered Blonde red finish</v>
+      </c>
+      <c r="N1082" t="str">
+        <v/>
+      </c>
+      <c r="O1082" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="str">
+        <v>MHK1012-D001</v>
+      </c>
+      <c r="B1083" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1083" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1083" t="str">
+        <v>38105NP-BN-1/0-5U</v>
+      </c>
+      <c r="E1083" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1083" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1083" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1083" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1083" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1083" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1083" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1083" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1083" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1083" t="str">
+        <v/>
+      </c>
+      <c r="O1083" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v>MHK1012-D002</v>
+      </c>
+      <c r="B1084" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1084" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1084" t="str">
+        <v>38105NP-BN-1/0-25U</v>
+      </c>
+      <c r="E1084" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1084" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1084" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1084" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1084" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1084" t="str">
+        <v>25U</v>
+      </c>
+      <c r="K1084" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1084" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1084" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1084" t="str">
+        <v/>
+      </c>
+      <c r="O1084" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="str">
+        <v>MHK1012-D003</v>
+      </c>
+      <c r="B1085" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1085" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1085" t="str">
+        <v>38105NP-RB-1/0-5U</v>
+      </c>
+      <c r="E1085" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1085" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1085" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1085" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1085" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1085" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1085" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1085" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1085" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1085" t="str">
+        <v/>
+      </c>
+      <c r="O1085" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v>MHK1012-D004</v>
+      </c>
+      <c r="B1086" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1086" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1086" t="str">
+        <v>38105NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1086" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1086" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1086" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1086" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1086" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1086" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1086" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1086" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1086" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1086" t="str">
+        <v/>
+      </c>
+      <c r="O1086" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
+        <v>MHK1012-D005</v>
+      </c>
+      <c r="B1087" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1087" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1087" t="str">
+        <v>38105NP-BN-2/0-25U</v>
+      </c>
+      <c r="E1087" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1087" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1087" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1087" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1087" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1087" t="str">
+        <v>25U</v>
+      </c>
+      <c r="K1087" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1087" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1087" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1087" t="str">
+        <v/>
+      </c>
+      <c r="O1087" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v>MHK1012-D006</v>
+      </c>
+      <c r="B1088" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1088" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1088" t="str">
+        <v>38105NP-RB-2/0-5U</v>
+      </c>
+      <c r="E1088" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1088" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1088" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1088" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1088" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1088" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1088" t="str">
+        <v>2.50</v>
+      </c>
+      <c r="L1088" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1088" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1088" t="str">
+        <v/>
+      </c>
+      <c r="O1088" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v>MHK1012-D007</v>
+      </c>
+      <c r="B1089" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1089" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1089" t="str">
+        <v>38105NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1089" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1089" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1089" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1089" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1089" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1089" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1089" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1089" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1089" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1089" t="str">
+        <v/>
+      </c>
+      <c r="O1089" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v>MHK1012-D008</v>
+      </c>
+      <c r="B1090" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1090" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1090" t="str">
+        <v>38105NP-BN-3/0-25U</v>
+      </c>
+      <c r="E1090" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1090" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1090" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1090" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1090" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1090" t="str">
+        <v>25U</v>
+      </c>
+      <c r="K1090" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1090" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1090" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1090" t="str">
+        <v/>
+      </c>
+      <c r="O1090" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v>MHK1012-D009</v>
+      </c>
+      <c r="B1091" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1091" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1091" t="str">
+        <v>38105NP-RB-3/0-5U</v>
+      </c>
+      <c r="E1091" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1091" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1091" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1091" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1091" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1091" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1091" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1091" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1091" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1091" t="str">
+        <v/>
+      </c>
+      <c r="O1091" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v>MHK1012-D010</v>
+      </c>
+      <c r="B1092" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1092" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1092" t="str">
+        <v>38105NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1092" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1092" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1092" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1092" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1092" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1092" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1092" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1092" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1092" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1092" t="str">
+        <v/>
+      </c>
+      <c r="O1092" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="str">
+        <v>MHK1012-D011</v>
+      </c>
+      <c r="B1093" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1093" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1093" t="str">
+        <v>38105NP-BN-4/0-25U</v>
+      </c>
+      <c r="E1093" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1093" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1093" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1093" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1093" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1093" t="str">
+        <v>25U</v>
+      </c>
+      <c r="K1093" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1093" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1093" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1093" t="str">
+        <v/>
+      </c>
+      <c r="O1093" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v>MHK1012-D012</v>
+      </c>
+      <c r="B1094" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1094" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1094" t="str">
+        <v>38105NP-RB-4/0-5U</v>
+      </c>
+      <c r="E1094" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1094" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1094" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1094" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1094" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1094" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1094" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1094" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1094" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1094" t="str">
+        <v/>
+      </c>
+      <c r="O1094" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="str">
+        <v>MHK1012-D013</v>
+      </c>
+      <c r="B1095" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1095" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1095" t="str">
+        <v>38105NP-BN-5/0-5U</v>
+      </c>
+      <c r="E1095" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1095" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1095" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1095" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1095" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1095" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1095" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1095" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1095" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1095" t="str">
+        <v/>
+      </c>
+      <c r="O1095" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="str">
+        <v>MHK1012-D014</v>
+      </c>
+      <c r="B1096" t="str">
+        <v>MHK1012</v>
+      </c>
+      <c r="C1096" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1096" t="str">
+        <v>38105NP-BN-5/0-25U</v>
+      </c>
+      <c r="E1096" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1096" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1096" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1096" t="str">
+        <v>Black Nickel / Red Blonde</v>
+      </c>
+      <c r="I1096" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1096" t="str">
+        <v>25U</v>
+      </c>
+      <c r="K1096" t="str">
+        <v>20.99</v>
+      </c>
+      <c r="L1096" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1096" t="str">
+        <v>The Mustad Ultra Lock™ hooks feature Z-Bend offset hook that securely anchors a wide range of baits. It is an ideal choice for a wide range of large soft plastic lures such as shads, worms or swim baits. This hook is perfect for fishing around heavy cover targeting a wide variety of species, such as Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1096" t="str">
+        <v/>
+      </c>
+      <c r="O1096" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="str">
+        <v>MHK1013-D001</v>
+      </c>
+      <c r="B1097" t="str">
+        <v>MHK1013</v>
+      </c>
+      <c r="C1097" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1097" t="str">
+        <v>G34131NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1097" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1097" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1097" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1097" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1097" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1097" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1097" t="str">
+        <v>7.99</v>
+      </c>
+      <c r="L1097" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1097" t="str">
+        <v>The Grip-Pin Max hook is designed for soft plastic worms or swim baits. It features a coated PVC pin that securely anchors the front end of soft plastic lure with a "no slip, no slide" design. It is a perfect setup for fishing a weedless hook point for that really big fish. This strong hook makes a great platform for fishing near hard cover and vegetation, using a whole range of plastic softbaits. Fish it weightless or as a Texas or Drop Shot rig. The 2X strong hook, features a straight shank and wide bend for the best hooking and holding capacity. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight shank 2X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin Max™ Black Nickel finish</v>
+      </c>
+      <c r="N1097" t="str">
+        <v/>
+      </c>
+      <c r="O1097" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="str">
+        <v>MHK1013-D002</v>
+      </c>
+      <c r="B1098" t="str">
+        <v>MHK1013</v>
+      </c>
+      <c r="C1098" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1098" t="str">
+        <v>G34131NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1098" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1098" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1098" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1098" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1098" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1098" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1098" t="str">
+        <v>9.49</v>
+      </c>
+      <c r="L1098" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1098" t="str">
+        <v>The Grip-Pin Max hook is designed for soft plastic worms or swim baits. It features a coated PVC pin that securely anchors the front end of soft plastic lure with a "no slip, no slide" design. It is a perfect setup for fishing a weedless hook point for that really big fish. This strong hook makes a great platform for fishing near hard cover and vegetation, using a whole range of plastic softbaits. Fish it weightless or as a Texas or Drop Shot rig. The 2X strong hook, features a straight shank and wide bend for the best hooking and holding capacity. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight shank 2X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin Max™ Black Nickel finish</v>
+      </c>
+      <c r="N1098" t="str">
+        <v/>
+      </c>
+      <c r="O1098" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="str">
+        <v>MHK1013-D003</v>
+      </c>
+      <c r="B1099" t="str">
+        <v>MHK1013</v>
+      </c>
+      <c r="C1099" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1099" t="str">
+        <v>G34131NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1099" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1099" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1099" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1099" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1099" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1099" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1099" t="str">
+        <v>9.99</v>
+      </c>
+      <c r="L1099" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1099" t="str">
+        <v>The Grip-Pin Max hook is designed for soft plastic worms or swim baits. It features a coated PVC pin that securely anchors the front end of soft plastic lure with a "no slip, no slide" design. It is a perfect setup for fishing a weedless hook point for that really big fish. This strong hook makes a great platform for fishing near hard cover and vegetation, using a whole range of plastic softbaits. Fish it weightless or as a Texas or Drop Shot rig. The 2X strong hook, features a straight shank and wide bend for the best hooking and holding capacity. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight shank 2X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin Max™ Black Nickel finish</v>
+      </c>
+      <c r="N1099" t="str">
+        <v/>
+      </c>
+      <c r="O1099" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="str">
+        <v>MHK1013-D004</v>
+      </c>
+      <c r="B1100" t="str">
+        <v>MHK1013</v>
+      </c>
+      <c r="C1100" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1100" t="str">
+        <v>G34131NP-BN-5/0-5U</v>
+      </c>
+      <c r="E1100" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1100" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1100" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1100" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1100" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1100" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1100" t="str">
+        <v>10.49</v>
+      </c>
+      <c r="L1100" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1100" t="str">
+        <v>The Grip-Pin Max hook is designed for soft plastic worms or swim baits. It features a coated PVC pin that securely anchors the front end of soft plastic lure with a "no slip, no slide" design. It is a perfect setup for fishing a weedless hook point for that really big fish. This strong hook makes a great platform for fishing near hard cover and vegetation, using a whole range of plastic softbaits. Fish it weightless or as a Texas or Drop Shot rig. The 2X strong hook, features a straight shank and wide bend for the best hooking and holding capacity. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight shank 2X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin Max™ Black Nickel finish</v>
+      </c>
+      <c r="N1100" t="str">
+        <v/>
+      </c>
+      <c r="O1100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="str">
+        <v>MHK1013-D005</v>
+      </c>
+      <c r="B1101" t="str">
+        <v>MHK1013</v>
+      </c>
+      <c r="C1101" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1101" t="str">
+        <v>G34131NP-BN-6/0-5U</v>
+      </c>
+      <c r="E1101" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1101" t="str">
+        <v>Drop Shot</v>
+      </c>
+      <c r="G1101" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1101" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1101" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1101" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1101" t="str">
+        <v>5.25</v>
+      </c>
+      <c r="L1101" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1101" t="str">
+        <v>The Grip-Pin Max hook is designed for soft plastic worms or swim baits. It features a coated PVC pin that securely anchors the front end of soft plastic lure with a "no slip, no slide" design. It is a perfect setup for fishing a weedless hook point for that really big fish. This strong hook makes a great platform for fishing near hard cover and vegetation, using a whole range of plastic softbaits. Fish it weightless or as a Texas or Drop Shot rig. The 2X strong hook, features a straight shank and wide bend for the best hooking and holding capacity. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Straight shank 2X Strong Extra wide bend Ringed Eye Nor-Tempered Resin-coated Grip Pin Max™ Black Nickel finish</v>
+      </c>
+      <c r="N1101" t="str">
+        <v/>
+      </c>
+      <c r="O1101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="str">
+        <v>MHK1014-D001</v>
+      </c>
+      <c r="B1102" t="str">
+        <v>MHK1014</v>
+      </c>
+      <c r="C1102" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1102" t="str">
+        <v>37172NP-BN-2-4U</v>
+      </c>
+      <c r="E1102" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1102" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1102" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1102" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1102" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1102" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1102" t="str">
+        <v>7.49</v>
+      </c>
+      <c r="L1102" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1102" t="str">
+        <v>Fishing around heavy cover, roots or vegetation can prove a challenge without a weedless hook. The Mustad Impact™ Soft Plastic hook has a thin wire weedguard that prevents the hook from snagging. Perfect for tube bait soft lures. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Use it for Bass, Perch, Zander, Pike or Walleye. The hook features a build-in rear weight for perfect balancing. Black nickel finish. Weight: 1/32oz/0.9g. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedguard Nor-Tempered Built-in 1/32oz/0.9g weight Black Nickel finish</v>
+      </c>
+      <c r="N1102" t="str">
+        <v/>
+      </c>
+      <c r="O1102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="str">
+        <v>MHK1014-D002</v>
+      </c>
+      <c r="B1103" t="str">
+        <v>MHK1014</v>
+      </c>
+      <c r="C1103" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1103" t="str">
+        <v>37172NP-BN-1/0-4U</v>
+      </c>
+      <c r="E1103" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1103" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1103" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1103" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1103" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1103" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1103" t="str">
+        <v>7.49</v>
+      </c>
+      <c r="L1103" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1103" t="str">
+        <v>Fishing around heavy cover, roots or vegetation can prove a challenge without a weedless hook. The Mustad Impact™ Soft Plastic hook has a thin wire weedguard that prevents the hook from snagging. Perfect for tube bait soft lures. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Use it for Bass, Perch, Zander, Pike or Walleye. The hook features a build-in rear weight for perfect balancing. Black nickel finish. Weight: 1/32oz/0.9g. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedguard Nor-Tempered Built-in 1/32oz/0.9g weight Black Nickel finish</v>
+      </c>
+      <c r="N1103" t="str">
+        <v/>
+      </c>
+      <c r="O1103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="str">
+        <v>MHK1014-D003</v>
+      </c>
+      <c r="B1104" t="str">
+        <v>MHK1014</v>
+      </c>
+      <c r="C1104" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1104" t="str">
+        <v>37172NP-BN-2/0-4U</v>
+      </c>
+      <c r="E1104" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1104" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1104" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1104" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1104" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1104" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1104" t="str">
+        <v>6.99</v>
+      </c>
+      <c r="L1104" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1104" t="str">
+        <v>Fishing around heavy cover, roots or vegetation can prove a challenge without a weedless hook. The Mustad Impact™ Soft Plastic hook has a thin wire weedguard that prevents the hook from snagging. Perfect for tube bait soft lures. Rigging the tube lure is easy. Start by opening the weedguard and insert it into the rear of your tube bait. Continue till the tube is all the way through, making a straight presentation. Finish by resetting the weedguard on the point of the hook, never over the barb. Use it for Bass, Perch, Zander, Pike or Walleye. The hook features a build-in rear weight for perfect balancing. Black nickel finish. Weight: 1/32oz/0.9g. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedguard Nor-Tempered Built-in 1/32oz/0.9g weight Black Nickel finish</v>
+      </c>
+      <c r="N1104" t="str">
+        <v/>
+      </c>
+      <c r="O1104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="str">
+        <v>MHK1015-D001</v>
+      </c>
+      <c r="B1105" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="C1105" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1105" t="str">
+        <v>G38084NP-BN-4-5U</v>
+      </c>
+      <c r="E1105" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1105" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1105" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1105" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1105" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1105" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1105" t="str">
+        <v>6.99</v>
+      </c>
+      <c r="L1105" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1105" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1105" t="str">
+        <v/>
+      </c>
+      <c r="O1105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="str">
+        <v>MHK1015-D002</v>
+      </c>
+      <c r="B1106" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="C1106" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1106" t="str">
+        <v>G38084NP-BN-2-5U</v>
+      </c>
+      <c r="E1106" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1106" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1106" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1106" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1106" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1106" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1106" t="str">
+        <v>3.50</v>
+      </c>
+      <c r="L1106" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1106" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1106" t="str">
+        <v/>
+      </c>
+      <c r="O1106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="str">
+        <v>MHK1015-D003</v>
+      </c>
+      <c r="B1107" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="C1107" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1107" t="str">
+        <v>G38084NP-BN-1-5U</v>
+      </c>
+      <c r="E1107" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1107" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1107" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1107" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1107" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1107" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1107" t="str">
+        <v>6.99</v>
+      </c>
+      <c r="L1107" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1107" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1107" t="str">
+        <v/>
+      </c>
+      <c r="O1107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="str">
+        <v>MHK1015-D004</v>
+      </c>
+      <c r="B1108" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="C1108" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1108" t="str">
+        <v>G38084NP-BN-1/0-5U</v>
+      </c>
+      <c r="E1108" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1108" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1108" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1108" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1108" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1108" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1108" t="str">
+        <v>7.99</v>
+      </c>
+      <c r="L1108" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1108" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1108" t="str">
+        <v/>
+      </c>
+      <c r="O1108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="str">
+        <v>MHK1015-D005</v>
+      </c>
+      <c r="B1109" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="C1109" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1109" t="str">
+        <v>G38084NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1109" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1109" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1109" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1109" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1109" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1109" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1109" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1109" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1109" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1109" t="str">
+        <v/>
+      </c>
+      <c r="O1109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="str">
+        <v>MHK1015-D006</v>
+      </c>
+      <c r="B1110" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="C1110" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1110" t="str">
+        <v>G38084NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1110" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1110" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1110" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1110" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1110" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1110" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1110" t="str">
+        <v>9.49</v>
+      </c>
+      <c r="L1110" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1110" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1110" t="str">
+        <v/>
+      </c>
+      <c r="O1110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="str">
+        <v>MHK1015-D007</v>
+      </c>
+      <c r="B1111" t="str">
+        <v>MHK1015</v>
+      </c>
+      <c r="C1111" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1111" t="str">
+        <v>G38084NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1111" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1111" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1111" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1111" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1111" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1111" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1111" t="str">
+        <v>4.50</v>
+      </c>
+      <c r="L1111" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1111" t="str">
+        <v>The Kevin VanDam Soft Plastic hooks feature a molded resin pin that securely anchors a wide range of baits to the hook for a "no slip, no slide" design without tearing the soft bait. The extra wide bend hook is ideal choice for a wide range of soft plastic lures such as shads, worms or swim baits. It is a great choice for lightweight Texas rigs finesse presentation using thin line. Use it to catch Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend 2X Fine Wire Resin-coated Grip Pin® Ringed eye Forged Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1111" t="str">
+        <v/>
+      </c>
+      <c r="O1111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="str">
+        <v>MHK1016-D001</v>
+      </c>
+      <c r="B1112" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="C1112" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1112" t="str">
+        <v>38120AP-TX-2-6A</v>
+      </c>
+      <c r="E1112" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1112" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1112" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1112" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1112" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1112" t="str">
+        <v/>
+      </c>
+      <c r="K1112" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1112" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1112" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1112" t="str">
+        <v/>
+      </c>
+      <c r="O1112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="str">
+        <v>MHK1016-D002</v>
+      </c>
+      <c r="B1113" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="C1113" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1113" t="str">
+        <v>38120AP-TX-1-6A</v>
+      </c>
+      <c r="E1113" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1113" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1113" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1113" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1113" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1113" t="str">
+        <v/>
+      </c>
+      <c r="K1113" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1113" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1113" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1113" t="str">
+        <v/>
+      </c>
+      <c r="O1113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="str">
+        <v>MHK1016-D003</v>
+      </c>
+      <c r="B1114" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="C1114" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1114" t="str">
+        <v>38120AP-TX-1/0-6A</v>
+      </c>
+      <c r="E1114" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1114" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1114" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1114" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1114" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1114" t="str">
+        <v/>
+      </c>
+      <c r="K1114" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1114" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1114" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1114" t="str">
+        <v/>
+      </c>
+      <c r="O1114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="str">
+        <v>MHK1016-D004</v>
+      </c>
+      <c r="B1115" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="C1115" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1115" t="str">
+        <v>38120AP-TX-2/0-6A</v>
+      </c>
+      <c r="E1115" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1115" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1115" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1115" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1115" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1115" t="str">
+        <v/>
+      </c>
+      <c r="K1115" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1115" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1115" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1115" t="str">
+        <v/>
+      </c>
+      <c r="O1115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="str">
+        <v>MHK1016-D005</v>
+      </c>
+      <c r="B1116" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="C1116" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1116" t="str">
+        <v>38120AP-TX-3/0-6A</v>
+      </c>
+      <c r="E1116" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1116" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1116" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1116" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1116" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1116" t="str">
+        <v/>
+      </c>
+      <c r="K1116" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1116" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1116" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1116" t="str">
+        <v/>
+      </c>
+      <c r="O1116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="str">
+        <v>MHK1016-D006</v>
+      </c>
+      <c r="B1117" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="C1117" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1117" t="str">
+        <v>38120AP-TX-4/0-6A</v>
+      </c>
+      <c r="E1117" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1117" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1117" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1117" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1117" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1117" t="str">
+        <v/>
+      </c>
+      <c r="K1117" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1117" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1117" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1117" t="str">
+        <v/>
+      </c>
+      <c r="O1117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="str">
+        <v>MHK1016-D007</v>
+      </c>
+      <c r="B1118" t="str">
+        <v>MHK1016</v>
+      </c>
+      <c r="C1118" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1118" t="str">
+        <v>38120AP-TX-5/0-6A</v>
+      </c>
+      <c r="E1118" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1118" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1118" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1118" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1118" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1118" t="str">
+        <v/>
+      </c>
+      <c r="K1118" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1118" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1118" t="str">
+        <v>Mustad Assault Wide Gap Hook are built for landing lunkers. For versatile applications, these bass hooks are made for high hook-up ratios and secured hook-sets on big fish. The Z-bend and epoxy at the eye holds and protects soft plastics, perfect for wide gap hook applications like Texas and Carolina rigs, while also great when flipping. Mustad’s new Tak-bend places the point above the eye and at a more level angle with the bait, making the lure flush with the point and improving hook-sets compared to traditional bends. The aggressive bend gets plastic out of the way on a bite for quick penetration while also preserving strength and integrity when fish try to throw the hook. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1118" t="str">
+        <v/>
+      </c>
+      <c r="O1118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="str">
+        <v>MHK1017-D001</v>
+      </c>
+      <c r="B1119" t="str">
+        <v>MHK1017</v>
+      </c>
+      <c r="C1119" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1119" t="str">
+        <v>38106NP-BN-1/0-4U</v>
+      </c>
+      <c r="E1119" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1119" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1119" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1119" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1119" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1119" t="str">
+        <v/>
+      </c>
+      <c r="K1119" t="str">
+        <v>0.29</v>
+      </c>
+      <c r="L1119" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1119" t="str">
+        <v>The Mustad Ultra Lock™ Softbait Hook is perfect for delicate presentation of soft plastic worms. It is suitable for free water fishing with the hook exposed or weedless. The wide gap and offset shank provides excellent hooking and holding abilities. Fish it Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1119" t="str">
+        <v/>
+      </c>
+      <c r="O1119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="str">
+        <v>MHK1017-D002</v>
+      </c>
+      <c r="B1120" t="str">
+        <v>MHK1017</v>
+      </c>
+      <c r="C1120" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1120" t="str">
+        <v>38106NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1120" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1120" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1120" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1120" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1120" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1120" t="str">
+        <v/>
+      </c>
+      <c r="K1120" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1120" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1120" t="str">
+        <v>The Mustad Ultra Lock™ Softbait Hook is perfect for delicate presentation of soft plastic worms. It is suitable for free water fishing with the hook exposed or weedless. The wide gap and offset shank provides excellent hooking and holding abilities. Fish it Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1120" t="str">
+        <v/>
+      </c>
+      <c r="O1120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="str">
+        <v>MHK1017-D003</v>
+      </c>
+      <c r="B1121" t="str">
+        <v>MHK1017</v>
+      </c>
+      <c r="C1121" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1121" t="str">
+        <v>38106NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1121" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1121" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1121" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1121" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1121" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1121" t="str">
+        <v/>
+      </c>
+      <c r="K1121" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1121" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1121" t="str">
+        <v>The Mustad Ultra Lock™ Softbait Hook is perfect for delicate presentation of soft plastic worms. It is suitable for free water fishing with the hook exposed or weedless. The wide gap and offset shank provides excellent hooking and holding abilities. Fish it Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Extra wide bend Offset shank 1X Fine Wire Ringed eye Nor-Tempered</v>
+      </c>
+      <c r="N1121" t="str">
+        <v/>
+      </c>
+      <c r="O1121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="str">
+        <v>MHK1018-D001</v>
+      </c>
+      <c r="B1122" t="str">
+        <v>MHK1018</v>
+      </c>
+      <c r="C1122" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1122" t="str">
+        <v>39121NP-BN-1/0-5U</v>
+      </c>
+      <c r="E1122" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1122" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1122" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1122" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1122" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1122" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1122" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1122" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1122" t="str">
+        <v>The 1X fine wire Mustad Offset Worm Hook is designed for a wide range of soft plastic worms. Fish it Texas or Carolina Rig style or just free swimming. The hook features a round bend and a 90-degree Z-lock shoulder to hold baits firmly in place. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1122" t="str">
+        <v/>
+      </c>
+      <c r="O1122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="str">
+        <v>MHK1018-D002</v>
+      </c>
+      <c r="B1123" t="str">
+        <v>MHK1018</v>
+      </c>
+      <c r="C1123" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1123" t="str">
+        <v>39121NP-BN-2/0-5U</v>
+      </c>
+      <c r="E1123" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1123" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1123" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1123" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1123" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1123" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1123" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1123" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1123" t="str">
+        <v>The 1X fine wire Mustad Offset Worm Hook is designed for a wide range of soft plastic worms. Fish it Texas or Carolina Rig style or just free swimming. The hook features a round bend and a 90-degree Z-lock shoulder to hold baits firmly in place. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1123" t="str">
+        <v/>
+      </c>
+      <c r="O1123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="str">
+        <v>MHK1018-D003</v>
+      </c>
+      <c r="B1124" t="str">
+        <v>MHK1018</v>
+      </c>
+      <c r="C1124" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1124" t="str">
+        <v>39121NP-BN-3/0-5U</v>
+      </c>
+      <c r="E1124" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1124" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1124" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1124" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1124" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1124" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1124" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1124" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1124" t="str">
+        <v>The 1X fine wire Mustad Offset Worm Hook is designed for a wide range of soft plastic worms. Fish it Texas or Carolina Rig style or just free swimming. The hook features a round bend and a 90-degree Z-lock shoulder to hold baits firmly in place. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1124" t="str">
+        <v/>
+      </c>
+      <c r="O1124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="str">
+        <v>MHK1018-D004</v>
+      </c>
+      <c r="B1125" t="str">
+        <v>MHK1018</v>
+      </c>
+      <c r="C1125" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1125" t="str">
+        <v>39121NP-BN-4/0-5U</v>
+      </c>
+      <c r="E1125" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1125" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1125" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1125" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1125" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1125" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1125" t="str">
+        <v>4.99</v>
+      </c>
+      <c r="L1125" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1125" t="str">
+        <v>The 1X fine wire Mustad Offset Worm Hook is designed for a wide range of soft plastic worms. Fish it Texas or Carolina Rig style or just free swimming. The hook features a round bend and a 90-degree Z-lock shoulder to hold baits firmly in place. Use it for Bass, Perch, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point 1X Fine Wire Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1125" t="str">
+        <v/>
+      </c>
+      <c r="O1125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="str">
+        <v>MHK1019-D001</v>
+      </c>
+      <c r="B1126" t="str">
+        <v>MHK1019</v>
+      </c>
+      <c r="C1126" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1126" t="str">
+        <v>38122AP-TX-2/0-5A</v>
+      </c>
+      <c r="E1126" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1126" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1126" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1126" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1126" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1126" t="str">
+        <v/>
+      </c>
+      <c r="K1126" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1126" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1126" t="str">
+        <v>Fishing for big bass, monster pike, or any heavy predator among the grass calls for a tough hook built for weedless presentations. Featuring the latest precision hook point technology, the Assault Heavy hook is made for quick, solid hook-sets. Mustad's Assault Heavy hook offset the eye and point to allow perfect rigging with soft plastics with ease while holding the bait flush to the point for the ultimate weedless hook. These fish hooks offer the perfect bend for wide gap hook applications like Carolina rigs and Texas rigs as well as flipping thanks to the Z-bend and agressive AlphaPoint® red epoxy, which are designed to hold and protect lures. The combination of the aggressive bend and Mustad’s AlphaPoint® hook point technology culminates for a slimmer, sharper hook that penetrates quickly and efficiently. Using the same Opti-Angle sharpening technique as UltraPoint®, Mustad's latest hook point offers the durability Mustad known for. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1126" t="str">
+        <v/>
+      </c>
+      <c r="O1126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="str">
+        <v>MHK1019-D002</v>
+      </c>
+      <c r="B1127" t="str">
+        <v>MHK1019</v>
+      </c>
+      <c r="C1127" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1127" t="str">
+        <v>38122AP-TX-3/0-5A</v>
+      </c>
+      <c r="E1127" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1127" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1127" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1127" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1127" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1127" t="str">
+        <v/>
+      </c>
+      <c r="K1127" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1127" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1127" t="str">
+        <v>Fishing for big bass, monster pike, or any heavy predator among the grass calls for a tough hook built for weedless presentations. Featuring the latest precision hook point technology, the Assault Heavy hook is made for quick, solid hook-sets. Mustad's Assault Heavy hook offset the eye and point to allow perfect rigging with soft plastics with ease while holding the bait flush to the point for the ultimate weedless hook. These fish hooks offer the perfect bend for wide gap hook applications like Carolina rigs and Texas rigs as well as flipping thanks to the Z-bend and agressive AlphaPoint® red epoxy, which are designed to hold and protect lures. The combination of the aggressive bend and Mustad’s AlphaPoint® hook point technology culminates for a slimmer, sharper hook that penetrates quickly and efficiently. Using the same Opti-Angle sharpening technique as UltraPoint®, Mustad's latest hook point offers the durability Mustad known for. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1127" t="str">
+        <v/>
+      </c>
+      <c r="O1127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="str">
+        <v>MHK1019-D003</v>
+      </c>
+      <c r="B1128" t="str">
+        <v>MHK1019</v>
+      </c>
+      <c r="C1128" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1128" t="str">
+        <v>38122AP-TX-4/0-5A</v>
+      </c>
+      <c r="E1128" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1128" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1128" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1128" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1128" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1128" t="str">
+        <v/>
+      </c>
+      <c r="K1128" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1128" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1128" t="str">
+        <v>Fishing for big bass, monster pike, or any heavy predator among the grass calls for a tough hook built for weedless presentations. Featuring the latest precision hook point technology, the Assault Heavy hook is made for quick, solid hook-sets. Mustad's Assault Heavy hook offset the eye and point to allow perfect rigging with soft plastics with ease while holding the bait flush to the point for the ultimate weedless hook. These fish hooks offer the perfect bend for wide gap hook applications like Carolina rigs and Texas rigs as well as flipping thanks to the Z-bend and agressive AlphaPoint® red epoxy, which are designed to hold and protect lures. The combination of the aggressive bend and Mustad’s AlphaPoint® hook point technology culminates for a slimmer, sharper hook that penetrates quickly and efficiently. Using the same Opti-Angle sharpening technique as UltraPoint®, Mustad's latest hook point offers the durability Mustad known for. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1128" t="str">
+        <v/>
+      </c>
+      <c r="O1128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="str">
+        <v>MHK1019-D004</v>
+      </c>
+      <c r="B1129" t="str">
+        <v>MHK1019</v>
+      </c>
+      <c r="C1129" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1129" t="str">
+        <v>38122AP-TX-5/0-5A</v>
+      </c>
+      <c r="E1129" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1129" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1129" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1129" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1129" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1129" t="str">
+        <v/>
+      </c>
+      <c r="K1129" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1129" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1129" t="str">
+        <v>Fishing for big bass, monster pike, or any heavy predator among the grass calls for a tough hook built for weedless presentations. Featuring the latest precision hook point technology, the Assault Heavy hook is made for quick, solid hook-sets. Mustad's Assault Heavy hook offset the eye and point to allow perfect rigging with soft plastics with ease while holding the bait flush to the point for the ultimate weedless hook. These fish hooks offer the perfect bend for wide gap hook applications like Carolina rigs and Texas rigs as well as flipping thanks to the Z-bend and agressive AlphaPoint® red epoxy, which are designed to hold and protect lures. The combination of the aggressive bend and Mustad’s AlphaPoint® hook point technology culminates for a slimmer, sharper hook that penetrates quickly and efficiently. Using the same Opti-Angle sharpening technique as UltraPoint®, Mustad's latest hook point offers the durability Mustad known for. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1129" t="str">
+        <v/>
+      </c>
+      <c r="O1129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="str">
+        <v>MHK1019-D005</v>
+      </c>
+      <c r="B1130" t="str">
+        <v>MHK1019</v>
+      </c>
+      <c r="C1130" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1130" t="str">
+        <v>38122AP-TX-6/0-4A</v>
+      </c>
+      <c r="E1130" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1130" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1130" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1130" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1130" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1130" t="str">
+        <v/>
+      </c>
+      <c r="K1130" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1130" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1130" t="str">
+        <v>Fishing for big bass, monster pike, or any heavy predator among the grass calls for a tough hook built for weedless presentations. Featuring the latest precision hook point technology, the Assault Heavy hook is made for quick, solid hook-sets. Mustad's Assault Heavy hook offset the eye and point to allow perfect rigging with soft plastics with ease while holding the bait flush to the point for the ultimate weedless hook. These fish hooks offer the perfect bend for wide gap hook applications like Carolina rigs and Texas rigs as well as flipping thanks to the Z-bend and agressive AlphaPoint® red epoxy, which are designed to hold and protect lures. The combination of the aggressive bend and Mustad’s AlphaPoint® hook point technology culminates for a slimmer, sharper hook that penetrates quickly and efficiently. Using the same Opti-Angle sharpening technique as UltraPoint®, Mustad's latest hook point offers the durability Mustad known for. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1130" t="str">
+        <v/>
+      </c>
+      <c r="O1130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="str">
+        <v>MHK1019-D006</v>
+      </c>
+      <c r="B1131" t="str">
+        <v>MHK1019</v>
+      </c>
+      <c r="C1131" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1131" t="str">
+        <v>38122AP-TX-8/0-4A</v>
+      </c>
+      <c r="E1131" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1131" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1131" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1131" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1131" t="str">
+        <v>8/0</v>
+      </c>
+      <c r="J1131" t="str">
+        <v/>
+      </c>
+      <c r="K1131" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1131" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1131" t="str">
+        <v>Fishing for big bass, monster pike, or any heavy predator among the grass calls for a tough hook built for weedless presentations. Featuring the latest precision hook point technology, the Assault Heavy hook is made for quick, solid hook-sets. Mustad's Assault Heavy hook offset the eye and point to allow perfect rigging with soft plastics with ease while holding the bait flush to the point for the ultimate weedless hook. These fish hooks offer the perfect bend for wide gap hook applications like Carolina rigs and Texas rigs as well as flipping thanks to the Z-bend and agressive AlphaPoint® red epoxy, which are designed to hold and protect lures. The combination of the aggressive bend and Mustad’s AlphaPoint® hook point technology culminates for a slimmer, sharper hook that penetrates quickly and efficiently. Using the same Opti-Angle sharpening technique as UltraPoint®, Mustad's latest hook point offers the durability Mustad known for. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Z-Bend Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1131" t="str">
+        <v/>
+      </c>
+      <c r="O1131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="str">
+        <v>MHK1020-D001</v>
+      </c>
+      <c r="B1132" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1132" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1132" t="str">
+        <v>AG34045-TX-6-8A</v>
+      </c>
+      <c r="E1132" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1132" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1132" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1132" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1132" t="str">
+        <v>6</v>
+      </c>
+      <c r="J1132" t="str">
+        <v/>
+      </c>
+      <c r="K1132" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1132" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1132" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1132" t="str">
+        <v/>
+      </c>
+      <c r="O1132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="str">
+        <v>MHK1020-D002</v>
+      </c>
+      <c r="B1133" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1133" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1133" t="str">
+        <v>AG34045-TX-4-8A</v>
+      </c>
+      <c r="E1133" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1133" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1133" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1133" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1133" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1133" t="str">
+        <v/>
+      </c>
+      <c r="K1133" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1133" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1133" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1133" t="str">
+        <v/>
+      </c>
+      <c r="O1133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="str">
+        <v>MHK1020-D003</v>
+      </c>
+      <c r="B1134" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1134" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1134" t="str">
+        <v>AG34045-TX-2-8A</v>
+      </c>
+      <c r="E1134" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1134" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1134" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1134" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1134" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1134" t="str">
+        <v/>
+      </c>
+      <c r="K1134" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1134" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1134" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1134" t="str">
+        <v/>
+      </c>
+      <c r="O1134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="str">
+        <v>MHK1020-D004</v>
+      </c>
+      <c r="B1135" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1135" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1135" t="str">
+        <v>AG34045-1-5A</v>
+      </c>
+      <c r="E1135" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1135" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1135" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1135" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1135" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1135" t="str">
+        <v/>
+      </c>
+      <c r="K1135" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1135" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1135" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1135" t="str">
+        <v/>
+      </c>
+      <c r="O1135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="str">
+        <v>MHK1020-D005</v>
+      </c>
+      <c r="B1136" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1136" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1136" t="str">
+        <v>AG34045-1/0-5A</v>
+      </c>
+      <c r="E1136" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1136" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1136" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1136" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1136" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1136" t="str">
+        <v/>
+      </c>
+      <c r="K1136" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1136" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1136" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1136" t="str">
+        <v/>
+      </c>
+      <c r="O1136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="str">
+        <v>MHK1020-D006</v>
+      </c>
+      <c r="B1137" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1137" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1137" t="str">
+        <v>AG34045-2/0-5A</v>
+      </c>
+      <c r="E1137" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1137" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1137" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1137" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1137" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1137" t="str">
+        <v/>
+      </c>
+      <c r="K1137" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1137" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1137" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1137" t="str">
+        <v/>
+      </c>
+      <c r="O1137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v>MHK1020-D007</v>
+      </c>
+      <c r="B1138" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1138" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1138" t="str">
+        <v>AG34045-3/0-5A</v>
+      </c>
+      <c r="E1138" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1138" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1138" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1138" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1138" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1138" t="str">
+        <v/>
+      </c>
+      <c r="K1138" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1138" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1138" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1138" t="str">
+        <v/>
+      </c>
+      <c r="O1138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="str">
+        <v>MHK1020-D008</v>
+      </c>
+      <c r="B1139" t="str">
+        <v>MHK1020</v>
+      </c>
+      <c r="C1139" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1139" t="str">
+        <v>AG34045-4/0-5A</v>
+      </c>
+      <c r="E1139" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1139" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1139" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1139" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1139" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1139" t="str">
+        <v/>
+      </c>
+      <c r="K1139" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1139" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1139" t="str">
+        <v>The all-new Alpha-Grip baitholder pin holds soft plastics in place in the most secure way possible. The special angle and red epoxy in the eye ensures a solid hold when fishing in the weeds. For a dependable hook-up, the Finesse hook has a carefully crafted wide gap that resists being thrown by a thrashing Bass. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 1X Fine Alpha-Grip Ringed eye Forged Nor-Tempered</v>
+      </c>
+      <c r="N1139" t="str">
+        <v/>
+      </c>
+      <c r="O1139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="str">
+        <v>MHK1021-D001</v>
+      </c>
+      <c r="B1140" t="str">
+        <v>MHK1021</v>
+      </c>
+      <c r="C1140" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1140" t="str">
+        <v>W60403NP-TX-4-4U</v>
+      </c>
+      <c r="E1140" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1140" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1140" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1140" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1140" t="str">
+        <v>4</v>
+      </c>
+      <c r="J1140" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1140" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1140" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1140" t="str">
+        <v>In collaboration between Bass Tournament Pro's Jacob Powroznik and 24-times Bassmaster winner Kevin VanDam, Mustad introduces the TitanX Wacky / Neko Dropshot hook. The Mustad Weedless Wacky Hook comes with fluorocarbon weedguard attached giving the freedom for snag free fishing around structures and heavy weed. Designed with an extra-wide gap, which provides secure hookset. Rigging for wacky style is easy. Thread the hook point through the middle of your soft plastic worm so that both ends dangle on either side of the hook. If you want to reduce tearing many anglers use a rubber “O”-ring around the soft worm and secure the hook in that. The wacky style creates a lot of action to your bait, attraction the biggest Bass around. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedless Nor-Tempered TitanX finish</v>
+      </c>
+      <c r="N1140" t="str">
+        <v/>
+      </c>
+      <c r="O1140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="str">
+        <v>MHK1021-D002</v>
+      </c>
+      <c r="B1141" t="str">
+        <v>MHK1021</v>
+      </c>
+      <c r="C1141" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1141" t="str">
+        <v>W60403NP-TX-2-4U</v>
+      </c>
+      <c r="E1141" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1141" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1141" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1141" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1141" t="str">
+        <v>2</v>
+      </c>
+      <c r="J1141" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1141" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1141" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1141" t="str">
+        <v>In collaboration between Bass Tournament Pro's Jacob Powroznik and 24-times Bassmaster winner Kevin VanDam, Mustad introduces the TitanX Wacky / Neko Dropshot hook. The Mustad Weedless Wacky Hook comes with fluorocarbon weedguard attached giving the freedom for snag free fishing around structures and heavy weed. Designed with an extra-wide gap, which provides secure hookset. Rigging for wacky style is easy. Thread the hook point through the middle of your soft plastic worm so that both ends dangle on either side of the hook. If you want to reduce tearing many anglers use a rubber “O”-ring around the soft worm and secure the hook in that. The wacky style creates a lot of action to your bait, attraction the biggest Bass around. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedless Nor-Tempered TitanX finish</v>
+      </c>
+      <c r="N1141" t="str">
+        <v/>
+      </c>
+      <c r="O1141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="str">
+        <v>MHK1021-D003</v>
+      </c>
+      <c r="B1142" t="str">
+        <v>MHK1021</v>
+      </c>
+      <c r="C1142" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1142" t="str">
+        <v>W60403NP-TX-1-4U</v>
+      </c>
+      <c r="E1142" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1142" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1142" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1142" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1142" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1142" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1142" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1142" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1142" t="str">
+        <v>In collaboration between Bass Tournament Pro's Jacob Powroznik and 24-times Bassmaster winner Kevin VanDam, Mustad introduces the TitanX Wacky / Neko Dropshot hook. The Mustad Weedless Wacky Hook comes with fluorocarbon weedguard attached giving the freedom for snag free fishing around structures and heavy weed. Designed with an extra-wide gap, which provides secure hookset. Rigging for wacky style is easy. Thread the hook point through the middle of your soft plastic worm so that both ends dangle on either side of the hook. If you want to reduce tearing many anglers use a rubber “O”-ring around the soft worm and secure the hook in that. The wacky style creates a lot of action to your bait, attraction the biggest Bass around. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedless Nor-Tempered TitanX finish</v>
+      </c>
+      <c r="N1142" t="str">
+        <v/>
+      </c>
+      <c r="O1142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="str">
+        <v>MHK1021-D004</v>
+      </c>
+      <c r="B1143" t="str">
+        <v>MHK1021</v>
+      </c>
+      <c r="C1143" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1143" t="str">
+        <v>W60403NP-TX-1/0-4U</v>
+      </c>
+      <c r="E1143" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1143" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1143" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1143" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1143" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1143" t="str">
+        <v>4U</v>
+      </c>
+      <c r="K1143" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1143" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1143" t="str">
+        <v>In collaboration between Bass Tournament Pro's Jacob Powroznik and 24-times Bassmaster winner Kevin VanDam, Mustad introduces the TitanX Wacky / Neko Dropshot hook. The Mustad Weedless Wacky Hook comes with fluorocarbon weedguard attached giving the freedom for snag free fishing around structures and heavy weed. Designed with an extra-wide gap, which provides secure hookset. Rigging for wacky style is easy. Thread the hook point through the middle of your soft plastic worm so that both ends dangle on either side of the hook. If you want to reduce tearing many anglers use a rubber “O”-ring around the soft worm and secure the hook in that. The wacky style creates a lot of action to your bait, attraction the biggest Bass around. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedless Nor-Tempered TitanX finish</v>
+      </c>
+      <c r="N1143" t="str">
+        <v/>
+      </c>
+      <c r="O1143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="str">
+        <v>MHK1021-D005</v>
+      </c>
+      <c r="B1144" t="str">
+        <v>MHK1021</v>
+      </c>
+      <c r="C1144" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1144" t="str">
+        <v>W60403NP-TX-2/0-4U</v>
+      </c>
+      <c r="E1144" t="str">
+        <v>倒钓钩</v>
+      </c>
+      <c r="F1144" t="str">
+        <v>Wacky</v>
+      </c>
+      <c r="G1144" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1144" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1144" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1144" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1144" t="str">
+        <v>6.49</v>
+      </c>
+      <c r="L1144" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1144" t="str">
+        <v>In collaboration between Bass Tournament Pro's Jacob Powroznik and 24-times Bassmaster winner Kevin VanDam, Mustad introduces the TitanX Wacky / Neko Dropshot hook. The Mustad Weedless Wacky Hook comes with fluorocarbon weedguard attached giving the freedom for snag free fishing around structures and heavy weed. Designed with an extra-wide gap, which provides secure hookset. Rigging for wacky style is easy. Thread the hook point through the middle of your soft plastic worm so that both ends dangle on either side of the hook. If you want to reduce tearing many anglers use a rubber “O”-ring around the soft worm and secure the hook in that. The wacky style creates a lot of action to your bait, attraction the biggest Bass around. 4.3 UltraPoint® Technology Opti-Angle Needle Point Ringed eye Weedless Nor-Tempered TitanX finish</v>
+      </c>
+      <c r="N1144" t="str">
+        <v/>
+      </c>
+      <c r="O1144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="str">
+        <v>MHK1022-D001</v>
+      </c>
+      <c r="B1145" t="str">
+        <v>MHK1022</v>
+      </c>
+      <c r="C1145" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1145" t="str">
+        <v>91768S-2/0-5U</v>
+      </c>
+      <c r="E1145" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1145" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1145" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1145" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1145" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1145" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1145" t="str">
+        <v>4.00</v>
+      </c>
+      <c r="L1145" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1145" t="str">
+        <v>The Impact™ Spring Keeper Hook is designed for Texas Rigging soft plastic swim baits, Paddel Tails or life-like fish imitations. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design without tearing the soft bait. It is ideal for fishing weedless with perfect presentation and hooking properties. The in-line hook eye provides perfect presentation, making your lure track straight in the water. It is a perfect setup for free water fishing with the hook exposed. Fish it weightless or with a sinker in front to get at the deeper swimming fish. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ringed eye Spring keeper Nor-Tempered</v>
+      </c>
+      <c r="N1145" t="str">
+        <v/>
+      </c>
+      <c r="O1145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="str">
+        <v>MHK1022-D002</v>
+      </c>
+      <c r="B1146" t="str">
+        <v>MHK1022</v>
+      </c>
+      <c r="C1146" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1146" t="str">
+        <v>91768S-3/0-5U</v>
+      </c>
+      <c r="E1146" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1146" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1146" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1146" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1146" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1146" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1146" t="str">
+        <v>4.00</v>
+      </c>
+      <c r="L1146" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1146" t="str">
+        <v>The Impact™ Spring Keeper Hook is designed for Texas Rigging soft plastic swim baits, Paddel Tails or life-like fish imitations. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design without tearing the soft bait. It is ideal for fishing weedless with perfect presentation and hooking properties. The in-line hook eye provides perfect presentation, making your lure track straight in the water. It is a perfect setup for free water fishing with the hook exposed. Fish it weightless or with a sinker in front to get at the deeper swimming fish. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ringed eye Spring keeper Nor-Tempered</v>
+      </c>
+      <c r="N1146" t="str">
+        <v/>
+      </c>
+      <c r="O1146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="str">
+        <v>MHK1022-D003</v>
+      </c>
+      <c r="B1147" t="str">
+        <v>MHK1022</v>
+      </c>
+      <c r="C1147" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1147" t="str">
+        <v>91768S-4/0-5U</v>
+      </c>
+      <c r="E1147" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1147" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1147" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1147" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1147" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1147" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1147" t="str">
+        <v>4.00</v>
+      </c>
+      <c r="L1147" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1147" t="str">
+        <v>The Impact™ Spring Keeper Hook is designed for Texas Rigging soft plastic swim baits, Paddel Tails or life-like fish imitations. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design without tearing the soft bait. It is ideal for fishing weedless with perfect presentation and hooking properties. The in-line hook eye provides perfect presentation, making your lure track straight in the water. It is a perfect setup for free water fishing with the hook exposed. Fish it weightless or with a sinker in front to get at the deeper swimming fish. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ringed eye Spring keeper Nor-Tempered</v>
+      </c>
+      <c r="N1147" t="str">
+        <v/>
+      </c>
+      <c r="O1147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="str">
+        <v>MHK1022-D004</v>
+      </c>
+      <c r="B1148" t="str">
+        <v>MHK1022</v>
+      </c>
+      <c r="C1148" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1148" t="str">
+        <v>91768S-5/0-5U</v>
+      </c>
+      <c r="E1148" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1148" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1148" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1148" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1148" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1148" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1148" t="str">
+        <v>4.00</v>
+      </c>
+      <c r="L1148" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1148" t="str">
+        <v>The Impact™ Spring Keeper Hook is designed for Texas Rigging soft plastic swim baits, Paddel Tails or life-like fish imitations. It features a molded resin pin that securely anchors the front end of the soft plastic lure with a "no slip, no slide" design without tearing the soft bait. It is ideal for fishing weedless with perfect presentation and hooking properties. The in-line hook eye provides perfect presentation, making your lure track straight in the water. It is a perfect setup for free water fishing with the hook exposed. Fish it weightless or with a sinker in front to get at the deeper swimming fish. Use it for Bass, Perch, Brown Trout, Rainbow Trout, Zander, Pike or Walleye. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ringed eye Spring keeper Nor-Tempered</v>
+      </c>
+      <c r="N1148" t="str">
+        <v/>
+      </c>
+      <c r="O1148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="str">
+        <v>MHK1023-D001</v>
+      </c>
+      <c r="B1149" t="str">
+        <v>MHK1023</v>
+      </c>
+      <c r="C1149" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1149" t="str">
+        <v>91768KH-BN-1/0-5U</v>
+      </c>
+      <c r="E1149" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1149" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1149" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1149" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1149" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1149" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1149" t="str">
+        <v>4.25</v>
+      </c>
+      <c r="L1149" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1149" t="str">
+        <v>The Impact™ Straight Keeper Hook feature a unique ridged gripper pin, offering a secure hold for your favorite soft plastic bait. Perfect for free water fishing with the hook exposed. The wide gap provides excellent hooking and holding abilities. Fish it weedless Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ridged gripper pin Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1149" t="str">
+        <v/>
+      </c>
+      <c r="O1149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="str">
+        <v>MHK1023-D002</v>
+      </c>
+      <c r="B1150" t="str">
+        <v>MHK1023</v>
+      </c>
+      <c r="C1150" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1150" t="str">
+        <v>91768KH-BN-2/0-5U</v>
+      </c>
+      <c r="E1150" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1150" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1150" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1150" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1150" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1150" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1150" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1150" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1150" t="str">
+        <v>The Impact™ Straight Keeper Hook feature a unique ridged gripper pin, offering a secure hold for your favorite soft plastic bait. Perfect for free water fishing with the hook exposed. The wide gap provides excellent hooking and holding abilities. Fish it weedless Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ridged gripper pin Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1150" t="str">
+        <v/>
+      </c>
+      <c r="O1150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="str">
+        <v>MHK1023-D003</v>
+      </c>
+      <c r="B1151" t="str">
+        <v>MHK1023</v>
+      </c>
+      <c r="C1151" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1151" t="str">
+        <v>91768KH-BN-3/0-5U</v>
+      </c>
+      <c r="E1151" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1151" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1151" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1151" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1151" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1151" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1151" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1151" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1151" t="str">
+        <v>The Impact™ Straight Keeper Hook feature a unique ridged gripper pin, offering a secure hold for your favorite soft plastic bait. Perfect for free water fishing with the hook exposed. The wide gap provides excellent hooking and holding abilities. Fish it weedless Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ridged gripper pin Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1151" t="str">
+        <v/>
+      </c>
+      <c r="O1151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="str">
+        <v>MHK1023-D004</v>
+      </c>
+      <c r="B1152" t="str">
+        <v>MHK1023</v>
+      </c>
+      <c r="C1152" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1152" t="str">
+        <v>91768KH-BN-4/0-5U</v>
+      </c>
+      <c r="E1152" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1152" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1152" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1152" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1152" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1152" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1152" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1152" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1152" t="str">
+        <v>The Impact™ Straight Keeper Hook feature a unique ridged gripper pin, offering a secure hold for your favorite soft plastic bait. Perfect for free water fishing with the hook exposed. The wide gap provides excellent hooking and holding abilities. Fish it weedless Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ridged gripper pin Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1152" t="str">
+        <v/>
+      </c>
+      <c r="O1152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="str">
+        <v>MHK1023-D005</v>
+      </c>
+      <c r="B1153" t="str">
+        <v>MHK1023</v>
+      </c>
+      <c r="C1153" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1153" t="str">
+        <v>91768KH-BN-5/0-5U</v>
+      </c>
+      <c r="E1153" t="str">
+        <v>曲柄钩</v>
+      </c>
+      <c r="F1153" t="str">
+        <v>Offset / Wide Gap</v>
+      </c>
+      <c r="G1153" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1153" t="str">
+        <v>Black Nickel</v>
+      </c>
+      <c r="I1153" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1153" t="str">
+        <v>5U</v>
+      </c>
+      <c r="K1153" t="str">
+        <v>8.99</v>
+      </c>
+      <c r="L1153" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1153" t="str">
+        <v>The Impact™ Straight Keeper Hook feature a unique ridged gripper pin, offering a secure hold for your favorite soft plastic bait. Perfect for free water fishing with the hook exposed. The wide gap provides excellent hooking and holding abilities. Fish it weedless Texas or Carolina Rig style or just un-weighted. Use it for Bass, Perch, Zander, Pike or Walleye. Coated with Mustad's own Black Nickel finish, which is 4 times as rust resistant as traditional Black Nickel. 4.3 UltraPoint® Technology Opti-Angle Needle Point Wide Gap Ridged gripper pin Ringed eye Nor-Tempered Black Nickel finish</v>
+      </c>
+      <c r="N1153" t="str">
+        <v/>
+      </c>
+      <c r="O1153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="str">
+        <v>MHK1024-D001</v>
+      </c>
+      <c r="B1154" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1154" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1154" t="str">
+        <v>91700S-TX-1-4A</v>
+      </c>
+      <c r="E1154" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1154" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1154" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1154" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1154" t="str">
+        <v>1</v>
+      </c>
+      <c r="J1154" t="str">
+        <v/>
+      </c>
+      <c r="K1154" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1154" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1154" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1154" t="str">
+        <v/>
+      </c>
+      <c r="O1154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="str">
+        <v>MHK1024-D002</v>
+      </c>
+      <c r="B1155" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1155" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1155" t="str">
+        <v>91700S-TX-1/0-4A</v>
+      </c>
+      <c r="E1155" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1155" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1155" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1155" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1155" t="str">
+        <v>1/0</v>
+      </c>
+      <c r="J1155" t="str">
+        <v/>
+      </c>
+      <c r="K1155" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1155" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1155" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1155" t="str">
+        <v/>
+      </c>
+      <c r="O1155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="str">
+        <v>MHK1024-D003</v>
+      </c>
+      <c r="B1156" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1156" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1156" t="str">
+        <v>91700S-TX-2/0-4A</v>
+      </c>
+      <c r="E1156" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1156" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1156" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1156" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1156" t="str">
+        <v>2/0</v>
+      </c>
+      <c r="J1156" t="str">
+        <v/>
+      </c>
+      <c r="K1156" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1156" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1156" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1156" t="str">
+        <v/>
+      </c>
+      <c r="O1156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="str">
+        <v>MHK1024-D004</v>
+      </c>
+      <c r="B1157" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1157" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1157" t="str">
+        <v>91700S-TX-3/0-4A</v>
+      </c>
+      <c r="E1157" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1157" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1157" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1157" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1157" t="str">
+        <v>3/0</v>
+      </c>
+      <c r="J1157" t="str">
+        <v/>
+      </c>
+      <c r="K1157" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1157" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1157" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1157" t="str">
+        <v/>
+      </c>
+      <c r="O1157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="str">
+        <v>MHK1024-D005</v>
+      </c>
+      <c r="B1158" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1158" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1158" t="str">
+        <v>91700S-TX-4/0-4A</v>
+      </c>
+      <c r="E1158" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1158" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1158" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1158" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1158" t="str">
+        <v>4/0</v>
+      </c>
+      <c r="J1158" t="str">
+        <v/>
+      </c>
+      <c r="K1158" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1158" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1158" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1158" t="str">
+        <v/>
+      </c>
+      <c r="O1158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="str">
+        <v>MHK1024-D006</v>
+      </c>
+      <c r="B1159" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1159" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1159" t="str">
+        <v>91700S-TX-5/0-3A</v>
+      </c>
+      <c r="E1159" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1159" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1159" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1159" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1159" t="str">
+        <v>5/0</v>
+      </c>
+      <c r="J1159" t="str">
+        <v/>
+      </c>
+      <c r="K1159" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1159" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1159" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1159" t="str">
+        <v/>
+      </c>
+      <c r="O1159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="str">
+        <v>MHK1024-D007</v>
+      </c>
+      <c r="B1160" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1160" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1160" t="str">
+        <v>91700S-TX-6/0-3A</v>
+      </c>
+      <c r="E1160" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1160" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1160" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1160" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1160" t="str">
+        <v>6/0</v>
+      </c>
+      <c r="J1160" t="str">
+        <v/>
+      </c>
+      <c r="K1160" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1160" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1160" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1160" t="str">
+        <v/>
+      </c>
+      <c r="O1160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="str">
+        <v>MHK1024-D008</v>
+      </c>
+      <c r="B1161" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1161" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1161" t="str">
+        <v>91700S-TX-8/0-2A</v>
+      </c>
+      <c r="E1161" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1161" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1161" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1161" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1161" t="str">
+        <v>8/0</v>
+      </c>
+      <c r="J1161" t="str">
+        <v/>
+      </c>
+      <c r="K1161" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1161" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1161" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1161" t="str">
+        <v/>
+      </c>
+      <c r="O1161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="str">
+        <v>MHK1024-D009</v>
+      </c>
+      <c r="B1162" t="str">
+        <v>MHK1024</v>
+      </c>
+      <c r="C1162" t="str">
+        <v>Mustad</v>
+      </c>
+      <c r="D1162" t="str">
+        <v>91700S-TX-10/0-2A</v>
+      </c>
+      <c r="E1162" t="str">
+        <v>特种钩</v>
+      </c>
+      <c r="F1162" t="str">
+        <v>Bass Hook</v>
+      </c>
+      <c r="G1162" t="str">
+        <v>标准</v>
+      </c>
+      <c r="H1162" t="str">
+        <v>TitanX</v>
+      </c>
+      <c r="I1162" t="str">
+        <v>10/0</v>
+      </c>
+      <c r="J1162" t="str">
+        <v/>
+      </c>
+      <c r="K1162" t="str">
+        <v>5.49</v>
+      </c>
+      <c r="L1162" t="str">
+        <v>in_stock</v>
+      </c>
+      <c r="M1162" t="str">
+        <v>A new, aggressive shape sets the stage for a strong update to the Mustad soft plastics hook range. The sharp angle at the bend of the hook situates the lure flush with the point, for the ultimate weedless bait. With a strong spring rigged at the inline eye, the Inflitrator Swim Hook holds baits in place, bite after bite. With Mustad’s AlphaPoint® hook point technology, precision fishing takes advantage of the slimmer, ridiculously sharp point combined with the durability anglers expect from Mustad. The nano-thin TitanX finish with a sleek gun-metal look supports the sharpness of the hook and the smoothness maximizes penetration. 4.8 AlphaPoint® Technology Opti-Angle Needle Point 2X Strong Ringed eye Forged Nor-Tempered Features Alpha Spring™ keeper</v>
+      </c>
+      <c r="N1162" t="str">
+        <v/>
+      </c>
+      <c r="O1162" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O991"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O1162"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/hook_detail.xlsx
+++ b/GearSage-client/rate/excel/hook_detail.xlsx
@@ -48024,7 +48024,7 @@
         <v>10548NP-RB-8-10U</v>
       </c>
       <c r="E1014" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1014" t="str">
         <v>Offset / Wide Gap</v>
@@ -48071,7 +48071,7 @@
         <v>10548NP-RB-6-10U</v>
       </c>
       <c r="E1015" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1015" t="str">
         <v>Offset / Wide Gap</v>
@@ -48118,7 +48118,7 @@
         <v>10548NP-BN-4-10U</v>
       </c>
       <c r="E1016" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1016" t="str">
         <v>Offset / Wide Gap</v>
@@ -48165,7 +48165,7 @@
         <v>10548NP-RB-4-10U</v>
       </c>
       <c r="E1017" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1017" t="str">
         <v>Offset / Wide Gap</v>
@@ -48212,7 +48212,7 @@
         <v>10548NP-BN-2-10U</v>
       </c>
       <c r="E1018" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1018" t="str">
         <v>Offset / Wide Gap</v>
@@ -48259,7 +48259,7 @@
         <v>10548NP-RB-2-10U</v>
       </c>
       <c r="E1019" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1019" t="str">
         <v>Offset / Wide Gap</v>
@@ -48306,7 +48306,7 @@
         <v>10548NP-BN-1-10U</v>
       </c>
       <c r="E1020" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1020" t="str">
         <v>Offset / Wide Gap</v>
@@ -48353,7 +48353,7 @@
         <v>10548NP-RB-1-10U</v>
       </c>
       <c r="E1021" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1021" t="str">
         <v>Offset / Wide Gap</v>
@@ -48400,7 +48400,7 @@
         <v>10548NP-BN-1/0-6U</v>
       </c>
       <c r="E1022" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1022" t="str">
         <v>Offset / Wide Gap</v>
@@ -48447,7 +48447,7 @@
         <v>10548NP-RB-1/0-6U</v>
       </c>
       <c r="E1023" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1023" t="str">
         <v>Offset / Wide Gap</v>
@@ -48494,7 +48494,7 @@
         <v>10548NP-BN-2/0-6U</v>
       </c>
       <c r="E1024" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1024" t="str">
         <v>Offset / Wide Gap</v>
@@ -48541,7 +48541,7 @@
         <v>10548NP-RB-2/0-5U</v>
       </c>
       <c r="E1025" t="str">
-        <v>曲柄钩</v>
+        <v>倒钓钩</v>
       </c>
       <c r="F1025" t="str">
         <v>Offset / Wide Gap</v>

--- a/GearSage-client/rate/excel/hook_detail.xlsx
+++ b/GearSage-client/rate/excel/hook_detail.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
